--- a/預測結果與評估指標_kfold_mask幾何_長邊正規化_年齡性別.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_長邊正規化_年齡性別.xlsx
@@ -493,28 +493,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>603.14869999999996</v>
+        <v>606.4973</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>20.243392359526737</v>
+        <v>20.301925605048076</v>
       </c>
       <c r="F2" s="0">
-        <v>-2.7566076404732627</v>
+        <v>-2.6980743949519237</v>
       </c>
       <c r="G2" s="0">
-        <v>2.7566076404732627</v>
+        <v>2.6980743949519237</v>
       </c>
       <c r="H2" s="0">
-        <v>19.743392359526737</v>
+        <v>19.801925605048076</v>
       </c>
       <c r="I2" s="0">
-        <v>-3.2566076404732627</v>
+        <v>-3.1980743949519237</v>
       </c>
       <c r="J2" s="0">
-        <v>3.2566076404732627</v>
+        <v>3.1980743949519237</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -537,28 +537,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.62289999999996</v>
+        <v>609.20730000000003</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>20.344011365814904</v>
+        <v>20.425872105883002</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.65598863418509623</v>
+        <v>-0.57412789411699805</v>
       </c>
       <c r="G3" s="0">
-        <v>0.65598863418509623</v>
+        <v>0.57412789411699805</v>
       </c>
       <c r="H3" s="0">
-        <v>19.844011365814904</v>
+        <v>19.925872105883002</v>
       </c>
       <c r="I3" s="0">
-        <v>-1.1559886341850962</v>
+        <v>-1.0741278941169981</v>
       </c>
       <c r="J3" s="0">
-        <v>1.1559886341850962</v>
+        <v>1.0741278941169981</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -581,28 +581,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>773.59109999999998</v>
+        <v>755.06500000000005</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>23.656707970192201</v>
+        <v>23.488210382878023</v>
       </c>
       <c r="F4" s="0">
-        <v>0.15670797019220117</v>
+        <v>-0.011789617121976903</v>
       </c>
       <c r="G4" s="0">
-        <v>0.15670797019220117</v>
+        <v>0.011789617121976903</v>
       </c>
       <c r="H4" s="0">
-        <v>23.156707970192201</v>
+        <v>22.988210382878023</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.34329202980779883</v>
+        <v>-0.5117896171219769</v>
       </c>
       <c r="J4" s="0">
-        <v>0.34329202980779883</v>
+        <v>0.5117896171219769</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -625,28 +625,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.42529999999999</v>
+        <v>579.86080000000004</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>19.471932308953541</v>
+        <v>19.449636944758577</v>
       </c>
       <c r="F5" s="0">
-        <v>-1.5280676910464592</v>
+        <v>-1.5503630552414229</v>
       </c>
       <c r="G5" s="0">
-        <v>1.5280676910464592</v>
+        <v>1.5503630552414229</v>
       </c>
       <c r="H5" s="0">
-        <v>18.971932308953541</v>
+        <v>18.949636944758577</v>
       </c>
       <c r="I5" s="0">
-        <v>-2.0280676910464592</v>
+        <v>-2.0503630552414229</v>
       </c>
       <c r="J5" s="0">
-        <v>2.0280676910464592</v>
+        <v>2.0503630552414229</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -669,28 +669,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>632.08730000000003</v>
+        <v>634.26990000000001</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>20.652455665808947</v>
+        <v>21.018526222465859</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.84754433419105268</v>
+        <v>-0.48147377753414133</v>
       </c>
       <c r="G6" s="0">
-        <v>0.84754433419105268</v>
+        <v>0.48147377753414133</v>
       </c>
       <c r="H6" s="0">
-        <v>20.152455665808947</v>
+        <v>20.518526222465859</v>
       </c>
       <c r="I6" s="0">
-        <v>-1.3475443341910527</v>
+        <v>-0.98147377753414133</v>
       </c>
       <c r="J6" s="0">
-        <v>1.3475443341910527</v>
+        <v>0.98147377753414133</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -713,31 +713,31 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>720.98979999999995</v>
+        <v>691.86599999999999</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>22.59565657832427</v>
+        <v>21.83282523541558</v>
       </c>
       <c r="F7" s="0">
-        <v>0.59565657832427021</v>
+        <v>-0.16717476458441993</v>
       </c>
       <c r="G7" s="0">
-        <v>0.59565657832427021</v>
+        <v>0.16717476458441993</v>
       </c>
       <c r="H7" s="0">
-        <v>22.09565657832427</v>
+        <v>21.33282523541558</v>
       </c>
       <c r="I7" s="0">
-        <v>0.095656578324270214</v>
+        <v>-0.66717476458441993</v>
       </c>
       <c r="J7" s="0">
-        <v>0.095656578324270214</v>
+        <v>0.66717476458441993</v>
       </c>
       <c r="K7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="0">
         <v>5</v>
@@ -757,28 +757,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>758.05489999999998</v>
+        <v>763.82230000000004</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>23.549893397488763</v>
+        <v>23.707093340322256</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.4501066025112372</v>
+        <v>-1.2929066596777439</v>
       </c>
       <c r="G8" s="0">
-        <v>1.4501066025112372</v>
+        <v>1.2929066596777439</v>
       </c>
       <c r="H8" s="0">
-        <v>23.049893397488763</v>
+        <v>23.207093340322256</v>
       </c>
       <c r="I8" s="0">
-        <v>-1.9501066025112372</v>
+        <v>-1.7929066596777439</v>
       </c>
       <c r="J8" s="0">
-        <v>1.9501066025112372</v>
+        <v>1.7929066596777439</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -801,28 +801,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>607.71310000000005</v>
+        <v>612.55169999999998</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>19.665081932205098</v>
+        <v>20.409082814247952</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.83491806779490219</v>
+        <v>-0.090917185752047658</v>
       </c>
       <c r="G9" s="0">
-        <v>0.83491806779490219</v>
+        <v>0.090917185752047658</v>
       </c>
       <c r="H9" s="0">
-        <v>19.165081932205098</v>
+        <v>19.909082814247952</v>
       </c>
       <c r="I9" s="0">
-        <v>-1.3349180677949022</v>
+        <v>-0.59091718575204766</v>
       </c>
       <c r="J9" s="0">
-        <v>1.3349180677949022</v>
+        <v>0.59091718575204766</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -845,28 +845,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>641.99860000000001</v>
+        <v>647.83249999999998</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.063842576864648</v>
+        <v>21.46623154604734</v>
       </c>
       <c r="F10" s="0">
-        <v>0.063842576864647782</v>
+        <v>0.46623154604733941</v>
       </c>
       <c r="G10" s="0">
-        <v>0.063842576864647782</v>
+        <v>0.46623154604733941</v>
       </c>
       <c r="H10" s="0">
-        <v>20.563842576864648</v>
+        <v>20.96623154604734</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.43615742313535222</v>
+        <v>-0.033768453952660593</v>
       </c>
       <c r="J10" s="0">
-        <v>0.43615742313535222</v>
+        <v>0.033768453952660593</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -889,28 +889,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>463.59699999999998</v>
+        <v>468.75369999999998</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>18.955897968176256</v>
+        <v>19.001344455442759</v>
       </c>
       <c r="F11" s="0">
-        <v>0.95589796817625583</v>
+        <v>1.0013444554427586</v>
       </c>
       <c r="G11" s="0">
-        <v>0.95589796817625583</v>
+        <v>1.0013444554427586</v>
       </c>
       <c r="H11" s="0">
-        <v>18.455897968176256</v>
+        <v>18.501344455442759</v>
       </c>
       <c r="I11" s="0">
-        <v>0.45589796817625583</v>
+        <v>0.50134445544275863</v>
       </c>
       <c r="J11" s="0">
-        <v>0.45589796817625583</v>
+        <v>0.50134445544275863</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -933,28 +933,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>750.11170000000004</v>
+        <v>745.02800000000002</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>22.172236834712521</v>
+        <v>22.239280694413292</v>
       </c>
       <c r="F12" s="0">
-        <v>-2.8277631652874788</v>
+        <v>-2.7607193055867079</v>
       </c>
       <c r="G12" s="0">
-        <v>2.8277631652874788</v>
+        <v>2.7607193055867079</v>
       </c>
       <c r="H12" s="0">
-        <v>21.672236834712521</v>
+        <v>21.739280694413292</v>
       </c>
       <c r="I12" s="0">
-        <v>-3.3277631652874789</v>
+        <v>-3.2607193055867079</v>
       </c>
       <c r="J12" s="0">
-        <v>3.3277631652874789</v>
+        <v>3.2607193055867079</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -977,28 +977,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>675.26099999999997</v>
+        <v>674.10310000000004</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>21.579722284021855</v>
+        <v>21.506436506329617</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.92027771597814478</v>
+        <v>-0.99356349367038277</v>
       </c>
       <c r="G13" s="0">
-        <v>0.92027771597814478</v>
+        <v>0.99356349367038277</v>
       </c>
       <c r="H13" s="0">
-        <v>21.079722284021855</v>
+        <v>21.006436506329617</v>
       </c>
       <c r="I13" s="0">
-        <v>-1.4202777159781448</v>
+        <v>-1.4935634936703828</v>
       </c>
       <c r="J13" s="0">
-        <v>1.4202777159781448</v>
+        <v>1.4935634936703828</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1021,28 +1021,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>674.45989999999995</v>
+        <v>678.64329999999995</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.099264737476162</v>
+        <v>21.067602522881245</v>
       </c>
       <c r="F14" s="0">
-        <v>0.59926473747616171</v>
+        <v>0.56760252288124491</v>
       </c>
       <c r="G14" s="0">
-        <v>0.59926473747616171</v>
+        <v>0.56760252288124491</v>
       </c>
       <c r="H14" s="0">
-        <v>20.599264737476162</v>
+        <v>20.567602522881245</v>
       </c>
       <c r="I14" s="0">
-        <v>0.099264737476161713</v>
+        <v>0.067602522881244909</v>
       </c>
       <c r="J14" s="0">
-        <v>0.099264737476161713</v>
+        <v>0.067602522881244909</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1065,28 +1065,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>583.64300000000003</v>
+        <v>588.29200000000003</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>19.359341797900932</v>
+        <v>19.303306112168499</v>
       </c>
       <c r="F15" s="0">
-        <v>-0.14065820209906832</v>
+        <v>-0.19669388783150055</v>
       </c>
       <c r="G15" s="0">
-        <v>0.14065820209906832</v>
+        <v>0.19669388783150055</v>
       </c>
       <c r="H15" s="0">
-        <v>18.859341797900932</v>
+        <v>18.803306112168499</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.64065820209906832</v>
+        <v>-0.69669388783150055</v>
       </c>
       <c r="J15" s="0">
-        <v>0.64065820209906832</v>
+        <v>0.69669388783150055</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>0</v>
@@ -1109,28 +1109,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>617.06880000000001</v>
+        <v>618.86260000000004</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>22.822241218074716</v>
+        <v>21.515893519707134</v>
       </c>
       <c r="F16" s="0">
-        <v>3.3222412180747156</v>
+        <v>2.0158935197071344</v>
       </c>
       <c r="G16" s="0">
-        <v>3.3222412180747156</v>
+        <v>2.0158935197071344</v>
       </c>
       <c r="H16" s="0">
-        <v>22.322241218074716</v>
+        <v>21.015893519707134</v>
       </c>
       <c r="I16" s="0">
-        <v>2.8222412180747156</v>
+        <v>1.5158935197071344</v>
       </c>
       <c r="J16" s="0">
-        <v>2.8222412180747156</v>
+        <v>1.5158935197071344</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1153,28 +1153,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>565.14229999999998</v>
+        <v>557.87480000000005</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>19.601645581569045</v>
+        <v>19.43775344471856</v>
       </c>
       <c r="F17" s="0">
-        <v>1.1016455815690449</v>
+        <v>0.93775344471855959</v>
       </c>
       <c r="G17" s="0">
-        <v>1.1016455815690449</v>
+        <v>0.93775344471855959</v>
       </c>
       <c r="H17" s="0">
-        <v>19.101645581569045</v>
+        <v>18.93775344471856</v>
       </c>
       <c r="I17" s="0">
-        <v>0.60164558156904491</v>
+        <v>0.43775344471855959</v>
       </c>
       <c r="J17" s="0">
-        <v>0.60164558156904491</v>
+        <v>0.43775344471855959</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1197,28 +1197,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>726.14229999999998</v>
+        <v>734.02059999999995</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>22.073347562470108</v>
+        <v>22.174622123011655</v>
       </c>
       <c r="F18" s="0">
-        <v>-1.6766524375298921</v>
+        <v>-1.5753778769883446</v>
       </c>
       <c r="G18" s="0">
-        <v>1.6766524375298921</v>
+        <v>1.5753778769883446</v>
       </c>
       <c r="H18" s="0">
-        <v>21.573347562470108</v>
+        <v>21.674622123011655</v>
       </c>
       <c r="I18" s="0">
-        <v>-2.1766524375298921</v>
+        <v>-2.0753778769883446</v>
       </c>
       <c r="J18" s="0">
-        <v>2.1766524375298921</v>
+        <v>2.0753778769883446</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1241,28 +1241,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>668.60829999999999</v>
+        <v>674.8356</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>20.840127103314533</v>
+        <v>20.921687639306949</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.4098728966854672</v>
+        <v>-1.3283123606930509</v>
       </c>
       <c r="G19" s="0">
-        <v>1.4098728966854672</v>
+        <v>1.3283123606930509</v>
       </c>
       <c r="H19" s="0">
-        <v>20.340127103314533</v>
+        <v>20.421687639306949</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.9098728966854672</v>
+        <v>-1.8283123606930509</v>
       </c>
       <c r="J19" s="0">
-        <v>1.9098728966854672</v>
+        <v>1.8283123606930509</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1285,28 +1285,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>750.32280000000003</v>
+        <v>758.93589999999995</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>23.315681407578268</v>
+        <v>23.542005686399538</v>
       </c>
       <c r="F20" s="0">
-        <v>-2.1843185924217323</v>
+        <v>-1.9579943136004623</v>
       </c>
       <c r="G20" s="0">
-        <v>2.1843185924217323</v>
+        <v>1.9579943136004623</v>
       </c>
       <c r="H20" s="0">
-        <v>22.815681407578268</v>
+        <v>23.042005686399538</v>
       </c>
       <c r="I20" s="0">
-        <v>-2.6843185924217323</v>
+        <v>-2.4579943136004623</v>
       </c>
       <c r="J20" s="0">
-        <v>2.6843185924217323</v>
+        <v>2.4579943136004623</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1329,28 +1329,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>526.39779999999996</v>
+        <v>530.03160000000003</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>17.973133309013804</v>
+        <v>18.006907341121739</v>
       </c>
       <c r="F21" s="0">
-        <v>-4.5268666909861963</v>
+        <v>-4.4930926588782611</v>
       </c>
       <c r="G21" s="0">
-        <v>4.5268666909861963</v>
+        <v>4.4930926588782611</v>
       </c>
       <c r="H21" s="0">
-        <v>17.473133309013804</v>
+        <v>17.506907341121739</v>
       </c>
       <c r="I21" s="0">
-        <v>-5.0268666909861963</v>
+        <v>-4.9930926588782611</v>
       </c>
       <c r="J21" s="0">
-        <v>5.0268666909861963</v>
+        <v>4.9930926588782611</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1373,28 +1373,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>622.22630000000004</v>
+        <v>619.3691</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.27469111529377</v>
+        <v>20.135000540300986</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.2253088847062301</v>
+        <v>-1.364999459699014</v>
       </c>
       <c r="G22" s="0">
-        <v>1.2253088847062301</v>
+        <v>1.364999459699014</v>
       </c>
       <c r="H22" s="0">
-        <v>19.77469111529377</v>
+        <v>19.635000540300986</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.7253088847062301</v>
+        <v>-1.864999459699014</v>
       </c>
       <c r="J22" s="0">
-        <v>1.7253088847062301</v>
+        <v>1.864999459699014</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1417,28 +1417,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>671.48209999999995</v>
+        <v>681.04340000000002</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.724505561191574</v>
+        <v>21.867104973931106</v>
       </c>
       <c r="F23" s="0">
-        <v>1.7245055611915738</v>
+        <v>1.8671049739311059</v>
       </c>
       <c r="G23" s="0">
-        <v>1.7245055611915738</v>
+        <v>1.8671049739311059</v>
       </c>
       <c r="H23" s="0">
-        <v>21.224505561191574</v>
+        <v>21.367104973931106</v>
       </c>
       <c r="I23" s="0">
-        <v>1.2245055611915738</v>
+        <v>1.3671049739311059</v>
       </c>
       <c r="J23" s="0">
-        <v>1.2245055611915738</v>
+        <v>1.3671049739311059</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1461,28 +1461,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>582.96010000000001</v>
+        <v>585.4384</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>19.553581706821511</v>
+        <v>19.799481298368136</v>
       </c>
       <c r="F24" s="0">
-        <v>0.053581706821510977</v>
+        <v>0.29948129836813564</v>
       </c>
       <c r="G24" s="0">
-        <v>0.053581706821510977</v>
+        <v>0.29948129836813564</v>
       </c>
       <c r="H24" s="0">
-        <v>19.053581706821511</v>
+        <v>19.299481298368136</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.44641829317848902</v>
+        <v>-0.20051870163186436</v>
       </c>
       <c r="J24" s="0">
-        <v>0.44641829317848902</v>
+        <v>0.20051870163186436</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>0</v>
@@ -1505,28 +1505,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.6952</v>
+        <v>581.173</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>19.807068061972768</v>
+        <v>19.830382849733255</v>
       </c>
       <c r="F25" s="0">
-        <v>1.3070680619727675</v>
+        <v>1.3303828497332546</v>
       </c>
       <c r="G25" s="0">
-        <v>1.3070680619727675</v>
+        <v>1.3303828497332546</v>
       </c>
       <c r="H25" s="0">
-        <v>19.307068061972768</v>
+        <v>19.330382849733255</v>
       </c>
       <c r="I25" s="0">
-        <v>0.80706806197276748</v>
+        <v>0.8303828497332546</v>
       </c>
       <c r="J25" s="0">
-        <v>0.80706806197276748</v>
+        <v>0.8303828497332546</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1549,28 +1549,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>689.21019999999999</v>
+        <v>692.99239999999998</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>21.931185552280326</v>
+        <v>22.000671636359716</v>
       </c>
       <c r="F26" s="0">
-        <v>0.68118555228032562</v>
+        <v>0.75067163635971568</v>
       </c>
       <c r="G26" s="0">
-        <v>0.68118555228032562</v>
+        <v>0.75067163635971568</v>
       </c>
       <c r="H26" s="0">
-        <v>21.431185552280326</v>
+        <v>21.500671636359716</v>
       </c>
       <c r="I26" s="0">
-        <v>0.18118555228032562</v>
+        <v>0.25067163635971568</v>
       </c>
       <c r="J26" s="0">
-        <v>0.18118555228032562</v>
+        <v>0.25067163635971568</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1593,28 +1593,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>641.4787</v>
+        <v>643.06439999999998</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.827988322709043</v>
+        <v>20.765178518281285</v>
       </c>
       <c r="F27" s="0">
-        <v>1.577988322709043</v>
+        <v>1.5151785182812851</v>
       </c>
       <c r="G27" s="0">
-        <v>1.577988322709043</v>
+        <v>1.5151785182812851</v>
       </c>
       <c r="H27" s="0">
-        <v>20.327988322709043</v>
+        <v>20.265178518281285</v>
       </c>
       <c r="I27" s="0">
-        <v>1.077988322709043</v>
+        <v>1.0151785182812851</v>
       </c>
       <c r="J27" s="0">
-        <v>1.077988322709043</v>
+        <v>1.0151785182812851</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1637,28 +1637,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>684.71199999999999</v>
+        <v>679.27729999999997</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.491673125716225</v>
+        <v>21.224704528388006</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.25832687428377454</v>
+        <v>-0.52529547161199375</v>
       </c>
       <c r="G28" s="0">
-        <v>0.25832687428377454</v>
+        <v>0.52529547161199375</v>
       </c>
       <c r="H28" s="0">
-        <v>20.991673125716225</v>
+        <v>20.724704528388006</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.75832687428377454</v>
+        <v>-1.0252954716119938</v>
       </c>
       <c r="J28" s="0">
-        <v>0.75832687428377454</v>
+        <v>1.0252954716119938</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1681,28 +1681,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>527.95719999999994</v>
+        <v>531.55600000000004</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>19.141188540241842</v>
+        <v>19.121228006223184</v>
       </c>
       <c r="F29" s="0">
-        <v>-1.608811459758158</v>
+        <v>-1.6287719937768159</v>
       </c>
       <c r="G29" s="0">
-        <v>1.608811459758158</v>
+        <v>1.6287719937768159</v>
       </c>
       <c r="H29" s="0">
-        <v>18.641188540241842</v>
+        <v>18.621228006223184</v>
       </c>
       <c r="I29" s="0">
-        <v>-2.108811459758158</v>
+        <v>-2.1287719937768159</v>
       </c>
       <c r="J29" s="0">
-        <v>2.108811459758158</v>
+        <v>2.1287719937768159</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1725,28 +1725,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.46259999999995</v>
+        <v>685.61059999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>23.099445322888606</v>
+        <v>22.455521879021603</v>
       </c>
       <c r="F30" s="0">
-        <v>1.5994453228886059</v>
+        <v>0.95552187902160313</v>
       </c>
       <c r="G30" s="0">
-        <v>1.5994453228886059</v>
+        <v>0.95552187902160313</v>
       </c>
       <c r="H30" s="0">
-        <v>22.599445322888606</v>
+        <v>21.955521879021603</v>
       </c>
       <c r="I30" s="0">
-        <v>1.0994453228886059</v>
+        <v>0.45552187902160313</v>
       </c>
       <c r="J30" s="0">
-        <v>1.0994453228886059</v>
+        <v>0.45552187902160313</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>1</v>
@@ -1769,28 +1769,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>678.49210000000005</v>
+        <v>683.32539999999995</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>24.248571422612479</v>
+        <v>22.859851809126589</v>
       </c>
       <c r="F31" s="0">
-        <v>4.7485714226124785</v>
+        <v>3.3598518091265888</v>
       </c>
       <c r="G31" s="0">
-        <v>4.7485714226124785</v>
+        <v>3.3598518091265888</v>
       </c>
       <c r="H31" s="0">
-        <v>23.748571422612479</v>
+        <v>22.359851809126589</v>
       </c>
       <c r="I31" s="0">
-        <v>4.2485714226124785</v>
+        <v>2.8598518091265888</v>
       </c>
       <c r="J31" s="0">
-        <v>4.2485714226124785</v>
+        <v>2.8598518091265888</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1813,28 +1813,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>656.11270000000002</v>
+        <v>669.30840000000001</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>23.698362845495176</v>
+        <v>22.536664890691025</v>
       </c>
       <c r="F32" s="0">
-        <v>4.1983628454951756</v>
+        <v>3.036664890691025</v>
       </c>
       <c r="G32" s="0">
-        <v>4.1983628454951756</v>
+        <v>3.036664890691025</v>
       </c>
       <c r="H32" s="0">
-        <v>23.198362845495176</v>
+        <v>22.036664890691025</v>
       </c>
       <c r="I32" s="0">
-        <v>3.6983628454951756</v>
+        <v>2.536664890691025</v>
       </c>
       <c r="J32" s="0">
-        <v>3.6983628454951756</v>
+        <v>2.536664890691025</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1857,28 +1857,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>679.53120000000001</v>
+        <v>712.56219999999996</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>20.856360487484018</v>
+        <v>21.431331356548817</v>
       </c>
       <c r="F33" s="0">
-        <v>-0.14363951251598195</v>
+        <v>0.43133135654881727</v>
       </c>
       <c r="G33" s="0">
-        <v>0.14363951251598195</v>
+        <v>0.43133135654881727</v>
       </c>
       <c r="H33" s="0">
-        <v>20.356360487484018</v>
+        <v>20.931331356548817</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.64363951251598195</v>
+        <v>-0.068668643451182732</v>
       </c>
       <c r="J33" s="0">
-        <v>0.64363951251598195</v>
+        <v>0.068668643451182732</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>0</v>
@@ -1901,28 +1901,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.02089999999998</v>
+        <v>611.39670000000001</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>19.962400662727031</v>
+        <v>19.934442744989561</v>
       </c>
       <c r="F34" s="0">
-        <v>-0.28759933727296883</v>
+        <v>-0.31555725501043952</v>
       </c>
       <c r="G34" s="0">
-        <v>0.28759933727296883</v>
+        <v>0.31555725501043952</v>
       </c>
       <c r="H34" s="0">
-        <v>19.462400662727031</v>
+        <v>19.434442744989561</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.78759933727296883</v>
+        <v>-0.81555725501043952</v>
       </c>
       <c r="J34" s="0">
-        <v>0.78759933727296883</v>
+        <v>0.81555725501043952</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1945,28 +1945,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>623.09130000000005</v>
+        <v>622.68050000000005</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>20.299334783907355</v>
+        <v>20.274307969046678</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.200665216092645</v>
+        <v>-1.2256920309533221</v>
       </c>
       <c r="G35" s="0">
-        <v>1.200665216092645</v>
+        <v>1.2256920309533221</v>
       </c>
       <c r="H35" s="0">
-        <v>19.799334783907355</v>
+        <v>19.774307969046678</v>
       </c>
       <c r="I35" s="0">
-        <v>-1.700665216092645</v>
+        <v>-1.7256920309533221</v>
       </c>
       <c r="J35" s="0">
-        <v>1.700665216092645</v>
+        <v>1.7256920309533221</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1989,31 +1989,31 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>590.04459999999995</v>
+        <v>601.95100000000002</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>19.885815831512868</v>
+        <v>20.006615706764233</v>
       </c>
       <c r="F36" s="0">
-        <v>0.38581583151286836</v>
+        <v>0.50661570676423295</v>
       </c>
       <c r="G36" s="0">
-        <v>0.38581583151286836</v>
+        <v>0.50661570676423295</v>
       </c>
       <c r="H36" s="0">
-        <v>19.385815831512868</v>
+        <v>19.506615706764233</v>
       </c>
       <c r="I36" s="0">
-        <v>-0.11418416848713164</v>
+        <v>0.0066157067642329537</v>
       </c>
       <c r="J36" s="0">
-        <v>0.11418416848713164</v>
+        <v>0.0066157067642329537</v>
       </c>
       <c r="K36" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="0">
         <v>1</v>
@@ -2033,28 +2033,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.99620000000004</v>
+        <v>726.80799999999999</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>22.455471223162466</v>
+        <v>22.477249334699906</v>
       </c>
       <c r="F37" s="0">
-        <v>-2.5445287768375344</v>
+        <v>-2.5227506653000944</v>
       </c>
       <c r="G37" s="0">
-        <v>2.5445287768375344</v>
+        <v>2.5227506653000944</v>
       </c>
       <c r="H37" s="0">
-        <v>21.955471223162466</v>
+        <v>21.977249334699906</v>
       </c>
       <c r="I37" s="0">
-        <v>-3.0445287768375344</v>
+        <v>-3.0227506653000944</v>
       </c>
       <c r="J37" s="0">
-        <v>3.0445287768375344</v>
+        <v>3.0227506653000944</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2077,28 +2077,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>600.44100000000003</v>
+        <v>599.73789999999997</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>19.900249370769664</v>
+        <v>19.828035886203477</v>
       </c>
       <c r="F38" s="0">
-        <v>0.90024937076966438</v>
+        <v>0.82803588620347668</v>
       </c>
       <c r="G38" s="0">
-        <v>0.90024937076966438</v>
+        <v>0.82803588620347668</v>
       </c>
       <c r="H38" s="0">
-        <v>19.400249370769664</v>
+        <v>19.328035886203477</v>
       </c>
       <c r="I38" s="0">
-        <v>0.40024937076966438</v>
+        <v>0.32803588620347668</v>
       </c>
       <c r="J38" s="0">
-        <v>0.40024937076966438</v>
+        <v>0.32803588620347668</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2121,28 +2121,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>692.81489999999997</v>
+        <v>700.04589999999996</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>21.554143421635548</v>
+        <v>21.528516750683217</v>
       </c>
       <c r="F39" s="0">
-        <v>2.5541434216355476</v>
+        <v>2.5285167506832167</v>
       </c>
       <c r="G39" s="0">
-        <v>2.5541434216355476</v>
+        <v>2.5285167506832167</v>
       </c>
       <c r="H39" s="0">
-        <v>21.054143421635548</v>
+        <v>21.028516750683217</v>
       </c>
       <c r="I39" s="0">
-        <v>2.0541434216355476</v>
+        <v>2.0285167506832167</v>
       </c>
       <c r="J39" s="0">
-        <v>2.0541434216355476</v>
+        <v>2.0285167506832167</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2165,28 +2165,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>777.77840000000003</v>
+        <v>776.98199999999997</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>23.530711656035059</v>
+        <v>22.990680354724027</v>
       </c>
       <c r="F40" s="0">
-        <v>2.5307116560350593</v>
+        <v>1.9906803547240273</v>
       </c>
       <c r="G40" s="0">
-        <v>2.5307116560350593</v>
+        <v>1.9906803547240273</v>
       </c>
       <c r="H40" s="0">
-        <v>23.030711656035059</v>
+        <v>22.490680354724027</v>
       </c>
       <c r="I40" s="0">
-        <v>2.0307116560350593</v>
+        <v>1.4906803547240273</v>
       </c>
       <c r="J40" s="0">
-        <v>2.0307116560350593</v>
+        <v>1.4906803547240273</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>1</v>
@@ -2209,28 +2209,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>666.36320000000001</v>
+        <v>673.32410000000004</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>20.896334020749791</v>
+        <v>20.977325833942544</v>
       </c>
       <c r="F41" s="0">
-        <v>0.39633402074979074</v>
+        <v>0.47732583394254391</v>
       </c>
       <c r="G41" s="0">
-        <v>0.39633402074979074</v>
+        <v>0.47732583394254391</v>
       </c>
       <c r="H41" s="0">
-        <v>20.396334020749791</v>
+        <v>20.477325833942544</v>
       </c>
       <c r="I41" s="0">
-        <v>-0.10366597925020926</v>
+        <v>-0.022674166057456091</v>
       </c>
       <c r="J41" s="0">
-        <v>0.10366597925020926</v>
+        <v>0.022674166057456091</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>0</v>
@@ -2253,28 +2253,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>518.52380000000005</v>
+        <v>526.36469999999997</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>19.29485570521539</v>
+        <v>19.30938198748332</v>
       </c>
       <c r="F42" s="0">
-        <v>0.044855705215390174</v>
+        <v>0.059381987483320131</v>
       </c>
       <c r="G42" s="0">
-        <v>0.044855705215390174</v>
+        <v>0.059381987483320131</v>
       </c>
       <c r="H42" s="0">
-        <v>18.79485570521539</v>
+        <v>18.80938198748332</v>
       </c>
       <c r="I42" s="0">
-        <v>-0.45514429478460983</v>
+        <v>-0.44061801251667987</v>
       </c>
       <c r="J42" s="0">
-        <v>0.45514429478460983</v>
+        <v>0.44061801251667987</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>0</v>
@@ -2297,28 +2297,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>582.97400000000005</v>
+        <v>586.85530000000006</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>19.52044787983878</v>
+        <v>19.524304762220524</v>
       </c>
       <c r="F43" s="0">
-        <v>-0.47955212016121962</v>
+        <v>-0.47569523777947609</v>
       </c>
       <c r="G43" s="0">
-        <v>0.47955212016121962</v>
+        <v>0.47569523777947609</v>
       </c>
       <c r="H43" s="0">
-        <v>19.02044787983878</v>
+        <v>19.024304762220524</v>
       </c>
       <c r="I43" s="0">
-        <v>-0.97955212016121962</v>
+        <v>-0.97569523777947609</v>
       </c>
       <c r="J43" s="0">
-        <v>0.97955212016121962</v>
+        <v>0.97569523777947609</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>0</v>
@@ -2341,28 +2341,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>657.05769999999996</v>
+        <v>663.21749999999997</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>21.221037659603589</v>
+        <v>21.242274607514428</v>
       </c>
       <c r="F44" s="0">
-        <v>1.2210376596035886</v>
+        <v>1.2422746075144282</v>
       </c>
       <c r="G44" s="0">
-        <v>1.2210376596035886</v>
+        <v>1.2422746075144282</v>
       </c>
       <c r="H44" s="0">
-        <v>20.721037659603589</v>
+        <v>20.742274607514428</v>
       </c>
       <c r="I44" s="0">
-        <v>0.72103765960358857</v>
+        <v>0.7422746075144282</v>
       </c>
       <c r="J44" s="0">
-        <v>0.72103765960358857</v>
+        <v>0.7422746075144282</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2385,28 +2385,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>584.81910000000005</v>
+        <v>582.90459999999996</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>19.856041714447727</v>
+        <v>19.821742497353711</v>
       </c>
       <c r="F45" s="0">
-        <v>-0.14395828555227297</v>
+        <v>-0.17825750264628937</v>
       </c>
       <c r="G45" s="0">
-        <v>0.14395828555227297</v>
+        <v>0.17825750264628937</v>
       </c>
       <c r="H45" s="0">
-        <v>19.356041714447727</v>
+        <v>19.321742497353711</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.64395828555227297</v>
+        <v>-0.67825750264628937</v>
       </c>
       <c r="J45" s="0">
-        <v>0.64395828555227297</v>
+        <v>0.67825750264628937</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>0</v>
@@ -2429,31 +2429,31 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>728.66980000000001</v>
+        <v>732.64890000000003</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>22.363671975921388</v>
+        <v>22.543041164304</v>
       </c>
       <c r="F46" s="0">
-        <v>0.36367197592138822</v>
+        <v>0.54304116430400029</v>
       </c>
       <c r="G46" s="0">
-        <v>0.36367197592138822</v>
+        <v>0.54304116430400029</v>
       </c>
       <c r="H46" s="0">
-        <v>21.863671975921388</v>
+        <v>22.043041164304</v>
       </c>
       <c r="I46" s="0">
-        <v>-0.13632802407861178</v>
+        <v>0.04304116430400029</v>
       </c>
       <c r="J46" s="0">
-        <v>0.13632802407861178</v>
+        <v>0.04304116430400029</v>
       </c>
       <c r="K46" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="0">
         <v>3</v>
@@ -2473,28 +2473,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>697.34799999999996</v>
+        <v>704.21619999999996</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>22.066119923929577</v>
+        <v>22.20802713167609</v>
       </c>
       <c r="F47" s="0">
-        <v>0.066119923929576885</v>
+        <v>0.20802713167608999</v>
       </c>
       <c r="G47" s="0">
-        <v>0.066119923929576885</v>
+        <v>0.20802713167608999</v>
       </c>
       <c r="H47" s="0">
-        <v>21.566119923929577</v>
+        <v>21.70802713167609</v>
       </c>
       <c r="I47" s="0">
-        <v>-0.43388007607042312</v>
+        <v>-0.29197286832391001</v>
       </c>
       <c r="J47" s="0">
-        <v>0.43388007607042312</v>
+        <v>0.29197286832391001</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2517,28 +2517,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>696.77610000000004</v>
+        <v>707.67989999999998</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.589186734152033</v>
+        <v>21.790102945247494</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.4108132658479669</v>
+        <v>-1.2098970547525063</v>
       </c>
       <c r="G48" s="0">
-        <v>1.4108132658479669</v>
+        <v>1.2098970547525063</v>
       </c>
       <c r="H48" s="0">
-        <v>21.089186734152033</v>
+        <v>21.290102945247494</v>
       </c>
       <c r="I48" s="0">
-        <v>-1.9108132658479668</v>
+        <v>-1.7098970547525063</v>
       </c>
       <c r="J48" s="0">
-        <v>1.9108132658479668</v>
+        <v>1.7098970547525063</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2561,28 +2561,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>664.47260000000006</v>
+        <v>666.81700000000001</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>20.840464702896256</v>
+        <v>20.856283137567218</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.90953529710374426</v>
+        <v>-0.89371686243278248</v>
       </c>
       <c r="G49" s="0">
-        <v>0.90953529710374426</v>
+        <v>0.89371686243278248</v>
       </c>
       <c r="H49" s="0">
-        <v>20.340464702896256</v>
+        <v>20.356283137567218</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.4095352971037443</v>
+        <v>-1.3937168624327825</v>
       </c>
       <c r="J49" s="0">
-        <v>1.4095352971037443</v>
+        <v>1.3937168624327825</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2605,28 +2605,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>686.67639999999995</v>
+        <v>688.77390000000003</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.526037636388715</v>
+        <v>21.42663746000801</v>
       </c>
       <c r="F50" s="0">
-        <v>0.026037636388714702</v>
+        <v>-0.073362539991990161</v>
       </c>
       <c r="G50" s="0">
-        <v>0.026037636388714702</v>
+        <v>0.073362539991990161</v>
       </c>
       <c r="H50" s="0">
-        <v>21.026037636388715</v>
+        <v>20.92663746000801</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.4739623636112853</v>
+        <v>-0.57336253999199016</v>
       </c>
       <c r="J50" s="0">
-        <v>0.4739623636112853</v>
+        <v>0.57336253999199016</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2649,28 +2649,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>616.17359999999997</v>
+        <v>615.82560000000001</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>20.045933089478979</v>
+        <v>20.100556864549521</v>
       </c>
       <c r="F51" s="0">
-        <v>0.84593308947897938</v>
+        <v>0.90055686454952166</v>
       </c>
       <c r="G51" s="0">
-        <v>0.84593308947897938</v>
+        <v>0.90055686454952166</v>
       </c>
       <c r="H51" s="0">
-        <v>19.545933089478979</v>
+        <v>19.600556864549521</v>
       </c>
       <c r="I51" s="0">
-        <v>0.34593308947897938</v>
+        <v>0.40055686454952166</v>
       </c>
       <c r="J51" s="0">
-        <v>0.34593308947897938</v>
+        <v>0.40055686454952166</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2693,28 +2693,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>575.9733</v>
+        <v>568.91740000000004</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>19.676011175146776</v>
+        <v>19.599965195223376</v>
       </c>
       <c r="F52" s="0">
-        <v>2.1760111751467761</v>
+        <v>2.0999651952233762</v>
       </c>
       <c r="G52" s="0">
-        <v>2.1760111751467761</v>
+        <v>2.0999651952233762</v>
       </c>
       <c r="H52" s="0">
-        <v>19.176011175146776</v>
+        <v>19.099965195223376</v>
       </c>
       <c r="I52" s="0">
-        <v>1.6760111751467761</v>
+        <v>1.5999651952233762</v>
       </c>
       <c r="J52" s="0">
-        <v>1.6760111751467761</v>
+        <v>1.5999651952233762</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2737,28 +2737,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>589.5335</v>
+        <v>594.03499999999997</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>19.956188455911715</v>
+        <v>19.950104077343926</v>
       </c>
       <c r="F53" s="0">
-        <v>1.5561884559117161</v>
+        <v>1.5501040773439279</v>
       </c>
       <c r="G53" s="0">
-        <v>1.5561884559117161</v>
+        <v>1.5501040773439279</v>
       </c>
       <c r="H53" s="0">
-        <v>19.456188455911715</v>
+        <v>19.450104077343926</v>
       </c>
       <c r="I53" s="0">
-        <v>1.0561884559117161</v>
+        <v>1.0501040773439279</v>
       </c>
       <c r="J53" s="0">
-        <v>1.0561884559117161</v>
+        <v>1.0501040773439279</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2781,28 +2781,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>563.72389999999996</v>
+        <v>566.51940000000002</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>19.465430435137702</v>
+        <v>19.467938981154323</v>
       </c>
       <c r="F54" s="0">
-        <v>0.46543043513770144</v>
+        <v>0.46793898115432242</v>
       </c>
       <c r="G54" s="0">
-        <v>0.46543043513770144</v>
+        <v>0.46793898115432242</v>
       </c>
       <c r="H54" s="0">
-        <v>18.965430435137702</v>
+        <v>18.967938981154323</v>
       </c>
       <c r="I54" s="0">
-        <v>-0.034569564862298563</v>
+        <v>-0.03206101884567758</v>
       </c>
       <c r="J54" s="0">
-        <v>0.034569564862298563</v>
+        <v>0.03206101884567758</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>0</v>
@@ -2825,28 +2825,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.82780000000002</v>
+        <v>614.26739999999995</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>20.052362031309976</v>
+        <v>20.186651075991755</v>
       </c>
       <c r="F55" s="0">
-        <v>0.55236203130997552</v>
+        <v>0.68665107599175457</v>
       </c>
       <c r="G55" s="0">
-        <v>0.55236203130997552</v>
+        <v>0.68665107599175457</v>
       </c>
       <c r="H55" s="0">
-        <v>19.552362031309976</v>
+        <v>19.686651075991755</v>
       </c>
       <c r="I55" s="0">
-        <v>0.052362031309975521</v>
+        <v>0.18665107599175457</v>
       </c>
       <c r="J55" s="0">
-        <v>0.052362031309975521</v>
+        <v>0.18665107599175457</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2869,28 +2869,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>727.90769999999998</v>
+        <v>717.47789999999998</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>22.629494708872752</v>
+        <v>22.689381446539201</v>
       </c>
       <c r="F56" s="0">
-        <v>2.1294947088727518</v>
+        <v>2.1893814465392012</v>
       </c>
       <c r="G56" s="0">
-        <v>2.1294947088727518</v>
+        <v>2.1893814465392012</v>
       </c>
       <c r="H56" s="0">
-        <v>22.129494708872752</v>
+        <v>22.189381446539201</v>
       </c>
       <c r="I56" s="0">
-        <v>1.6294947088727518</v>
+        <v>1.6893814465392012</v>
       </c>
       <c r="J56" s="0">
-        <v>1.6294947088727518</v>
+        <v>1.6893814465392012</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>1</v>
@@ -2913,28 +2913,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>646.02480000000003</v>
+        <v>656.12369999999999</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>20.971765549018176</v>
+        <v>21.14239262800848</v>
       </c>
       <c r="F57" s="0">
-        <v>-0.028234450981823756</v>
+        <v>0.14239262800847996</v>
       </c>
       <c r="G57" s="0">
-        <v>0.028234450981823756</v>
+        <v>0.14239262800847996</v>
       </c>
       <c r="H57" s="0">
-        <v>20.471765549018176</v>
+        <v>20.64239262800848</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.52823445098182376</v>
+        <v>-0.35760737199152004</v>
       </c>
       <c r="J57" s="0">
-        <v>0.52823445098182376</v>
+        <v>0.35760737199152004</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2957,28 +2957,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>730.19860000000006</v>
+        <v>713.17060000000004</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>22.324271517446274</v>
+        <v>21.958003930618059</v>
       </c>
       <c r="F58" s="0">
-        <v>-1.1757284825537262</v>
+        <v>-1.5419960693819412</v>
       </c>
       <c r="G58" s="0">
-        <v>1.1757284825537262</v>
+        <v>1.5419960693819412</v>
       </c>
       <c r="H58" s="0">
-        <v>21.824271517446274</v>
+        <v>21.458003930618059</v>
       </c>
       <c r="I58" s="0">
-        <v>-1.6757284825537262</v>
+        <v>-2.0419960693819412</v>
       </c>
       <c r="J58" s="0">
-        <v>1.6757284825537262</v>
+        <v>2.0419960693819412</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -3001,31 +3001,31 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.77250000000004</v>
+        <v>675.12120000000004</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>20.590659523489897</v>
+        <v>21.809691270268896</v>
       </c>
       <c r="F59" s="0">
-        <v>0.090659523489897254</v>
+        <v>1.3096912702688961</v>
       </c>
       <c r="G59" s="0">
-        <v>0.090659523489897254</v>
+        <v>1.3096912702688961</v>
       </c>
       <c r="H59" s="0">
-        <v>20.090659523489897</v>
+        <v>21.309691270268896</v>
       </c>
       <c r="I59" s="0">
-        <v>-0.40934047651010275</v>
+        <v>0.80969127026889609</v>
       </c>
       <c r="J59" s="0">
-        <v>0.40934047651010275</v>
+        <v>0.80969127026889609</v>
       </c>
       <c r="K59" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="0">
         <v>2</v>
@@ -3045,28 +3045,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>695.50199999999995</v>
+        <v>689.68129999999997</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.744175359884181</v>
+        <v>21.575481779946344</v>
       </c>
       <c r="F60" s="0">
-        <v>0.24417535988418138</v>
+        <v>0.075481779946343863</v>
       </c>
       <c r="G60" s="0">
-        <v>0.24417535988418138</v>
+        <v>0.075481779946343863</v>
       </c>
       <c r="H60" s="0">
-        <v>21.244175359884181</v>
+        <v>21.075481779946344</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.25582464011581862</v>
+        <v>-0.42451822005365614</v>
       </c>
       <c r="J60" s="0">
-        <v>0.25582464011581862</v>
+        <v>0.42451822005365614</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3089,28 +3089,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>639.4633</v>
+        <v>646.9873</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.512523661150645</v>
+        <v>20.5296578299854</v>
       </c>
       <c r="F61" s="0">
-        <v>0.51252366115064518</v>
+        <v>0.52965782998539979</v>
       </c>
       <c r="G61" s="0">
-        <v>0.51252366115064518</v>
+        <v>0.52965782998539979</v>
       </c>
       <c r="H61" s="0">
-        <v>20.012523661150645</v>
+        <v>20.0296578299854</v>
       </c>
       <c r="I61" s="0">
-        <v>0.012523661150645182</v>
+        <v>0.029657829985399786</v>
       </c>
       <c r="J61" s="0">
-        <v>0.012523661150645182</v>
+        <v>0.029657829985399786</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3133,28 +3133,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>699.43420000000003</v>
+        <v>680.14350000000002</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.617422183350165</v>
+        <v>21.173560295212376</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.3825778166498353</v>
+        <v>-1.8264397047876244</v>
       </c>
       <c r="G62" s="0">
-        <v>1.3825778166498353</v>
+        <v>1.8264397047876244</v>
       </c>
       <c r="H62" s="0">
-        <v>21.117422183350165</v>
+        <v>20.673560295212376</v>
       </c>
       <c r="I62" s="0">
-        <v>-1.8825778166498353</v>
+        <v>-2.3264397047876244</v>
       </c>
       <c r="J62" s="0">
-        <v>1.8825778166498353</v>
+        <v>2.3264397047876244</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3177,28 +3177,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>683.36609999999996</v>
+        <v>675.0444</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.795735073327201</v>
+        <v>21.587177224707034</v>
       </c>
       <c r="F63" s="0">
-        <v>0.29573507332720084</v>
+        <v>0.087177224707033929</v>
       </c>
       <c r="G63" s="0">
-        <v>0.29573507332720084</v>
+        <v>0.087177224707033929</v>
       </c>
       <c r="H63" s="0">
-        <v>21.295735073327201</v>
+        <v>21.087177224707034</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.20426492667279916</v>
+        <v>-0.41282277529296607</v>
       </c>
       <c r="J63" s="0">
-        <v>0.20426492667279916</v>
+        <v>0.41282277529296607</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3221,28 +3221,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>635.10969999999998</v>
+        <v>638.85119999999995</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.555959239695955</v>
+        <v>20.517922328123262</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.9440407603040448</v>
+        <v>-1.9820776718767377</v>
       </c>
       <c r="G64" s="0">
-        <v>1.9440407603040448</v>
+        <v>1.9820776718767377</v>
       </c>
       <c r="H64" s="0">
-        <v>20.055959239695955</v>
+        <v>20.017922328123262</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.4440407603040448</v>
+        <v>-2.4820776718767377</v>
       </c>
       <c r="J64" s="0">
-        <v>2.4440407603040448</v>
+        <v>2.4820776718767377</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3265,28 +3265,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>594.92830000000004</v>
+        <v>595.31380000000001</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>19.84344457193539</v>
+        <v>19.94440481022745</v>
       </c>
       <c r="F65" s="0">
-        <v>0.59344457193538958</v>
+        <v>0.69440481022745004</v>
       </c>
       <c r="G65" s="0">
-        <v>0.59344457193538958</v>
+        <v>0.69440481022745004</v>
       </c>
       <c r="H65" s="0">
-        <v>19.34344457193539</v>
+        <v>19.44440481022745</v>
       </c>
       <c r="I65" s="0">
-        <v>0.093444571935389576</v>
+        <v>0.19440481022745004</v>
       </c>
       <c r="J65" s="0">
-        <v>0.093444571935389576</v>
+        <v>0.19440481022745004</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3309,28 +3309,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>672.91949999999997</v>
+        <v>698.0498</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.002031445680366</v>
+        <v>21.447023574722206</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.4979685543196339</v>
+        <v>-2.0529764252777945</v>
       </c>
       <c r="G66" s="0">
-        <v>2.4979685543196339</v>
+        <v>2.0529764252777945</v>
       </c>
       <c r="H66" s="0">
-        <v>20.502031445680366</v>
+        <v>20.947023574722206</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.9979685543196339</v>
+        <v>-2.5529764252777945</v>
       </c>
       <c r="J66" s="0">
-        <v>2.9979685543196339</v>
+        <v>2.5529764252777945</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3353,28 +3353,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>637.33479999999997</v>
+        <v>634.08339999999998</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>20.420792583283308</v>
+        <v>20.351278719564263</v>
       </c>
       <c r="F67" s="0">
-        <v>-1.0792074167166916</v>
+        <v>-1.148721280435737</v>
       </c>
       <c r="G67" s="0">
-        <v>1.0792074167166916</v>
+        <v>1.148721280435737</v>
       </c>
       <c r="H67" s="0">
-        <v>19.920792583283308</v>
+        <v>19.851278719564263</v>
       </c>
       <c r="I67" s="0">
-        <v>-1.5792074167166916</v>
+        <v>-1.648721280435737</v>
       </c>
       <c r="J67" s="0">
-        <v>1.5792074167166916</v>
+        <v>1.648721280435737</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3397,28 +3397,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>572.66319999999996</v>
+        <v>578.7296</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>19.964790704909674</v>
+        <v>20.028191805653481</v>
       </c>
       <c r="F68" s="0">
-        <v>0.96479070490967445</v>
+        <v>1.0281918056534813</v>
       </c>
       <c r="G68" s="0">
-        <v>0.96479070490967445</v>
+        <v>1.0281918056534813</v>
       </c>
       <c r="H68" s="0">
-        <v>19.464790704909674</v>
+        <v>19.528191805653481</v>
       </c>
       <c r="I68" s="0">
-        <v>0.46479070490967445</v>
+        <v>0.52819180565348134</v>
       </c>
       <c r="J68" s="0">
-        <v>0.46479070490967445</v>
+        <v>0.52819180565348134</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3479,16 +3479,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.2190000000000001</v>
+        <v>1.1619999999999999</v>
       </c>
       <c r="C2" s="0">
-        <v>1.6259999999999999</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="D2" s="0">
-        <v>0.23899999999999999</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="E2" s="0">
-        <v>0.023</v>
+        <v>-0.0070000000000000001</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3501,13 +3501,13 @@
         <v>0</v>
       </c>
       <c r="C3" s="0">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D3" s="0">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E3" s="0">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F3" s="0">
         <v>0</v>
@@ -3532,18 +3532,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.282</v>
+        <v>1.1930000000000001</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.47699999999999998</v>
+        <v>-0.50700000000000001</v>
       </c>
       <c r="F5" s="0">
-        <v>49.299999999999997</v>
+        <v>52.200000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>35.799999999999997</v>
+        <v>38.799999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -3551,16 +3551,16 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.1060000000000001</v>
+        <v>1.121</v>
       </c>
       <c r="C6" s="0">
-        <v>1.3999999999999999</v>
+        <v>1.417</v>
       </c>
       <c r="D6" s="0">
-        <v>0.38700000000000001</v>
+        <v>0.374</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.0040000000000000001</v>
+        <v>-0.0089999999999999993</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -3570,18 +3570,18 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.141</v>
+        <v>1.167</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
       <c r="E7" s="0">
-        <v>-0.504</v>
+        <v>-0.50900000000000001</v>
       </c>
       <c r="F7" s="0">
         <v>53.700000000000003</v>
       </c>
       <c r="G7" s="0">
-        <v>37.299999999999997</v>
+        <v>38.799999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -3663,9 +3663,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="true"/>
-    <col min="2" max="2" width="7.42578125" customWidth="true"/>
+    <col min="2" max="2" width="6.7109375" customWidth="true"/>
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
-    <col min="4" max="4" width="6.42578125" customWidth="true"/>
+    <col min="4" max="4" width="5.7109375" customWidth="true"/>
     <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
@@ -3691,13 +3691,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>9.9094999999999995</v>
+        <v>9.7431000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>1.7159</v>
+        <v>1.7477</v>
       </c>
       <c r="D2" s="0">
-        <v>5.7750000000000004</v>
+        <v>5.5750000000000002</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>113</v>
       </c>
       <c r="B3" s="0">
-        <v>0.017899999999999999</v>
+        <v>0.018100000000000002</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0025000000000000001</v>
+        <v>0.0025999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>7.0940000000000003</v>
+        <v>7.056</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>
@@ -3725,16 +3725,16 @@
         <v>114</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.015100000000000001</v>
+        <v>-0.016</v>
       </c>
       <c r="C4" s="0">
         <v>0.01</v>
       </c>
       <c r="D4" s="0">
-        <v>-1.5129999999999999</v>
+        <v>-1.6000000000000001</v>
       </c>
       <c r="E4" s="0">
-        <v>0.13519999999999999</v>
+        <v>0.11459999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3742,16 +3742,16 @@
         <v>115</v>
       </c>
       <c r="B5" s="0">
-        <v>0.379</v>
+        <v>0.4229</v>
       </c>
       <c r="C5" s="0">
-        <v>0.3372</v>
+        <v>0.3377</v>
       </c>
       <c r="D5" s="0">
-        <v>1.1240000000000001</v>
+        <v>1.252</v>
       </c>
       <c r="E5" s="0">
-        <v>0.26529999999999998</v>
+        <v>0.21510000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/預測結果與評估指標_kfold_mask幾何_長邊正規化_年齡性別.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_長邊正規化_年齡性別.xlsx
@@ -493,28 +493,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>606.4973</v>
+        <v>610.42669999999998</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>20.301925605048076</v>
+        <v>20.221900509667446</v>
       </c>
       <c r="F2" s="0">
-        <v>-2.6980743949519237</v>
+        <v>-2.7780994903325542</v>
       </c>
       <c r="G2" s="0">
-        <v>2.6980743949519237</v>
+        <v>2.7780994903325542</v>
       </c>
       <c r="H2" s="0">
-        <v>19.801925605048076</v>
+        <v>19.721900509667446</v>
       </c>
       <c r="I2" s="0">
-        <v>-3.1980743949519237</v>
+        <v>-3.2780994903325542</v>
       </c>
       <c r="J2" s="0">
-        <v>3.1980743949519237</v>
+        <v>3.2780994903325542</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -537,28 +537,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>609.20730000000003</v>
+        <v>618.74630000000002</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>20.425872105883002</v>
+        <v>20.56584236986571</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.57412789411699805</v>
+        <v>-0.43415763013429043</v>
       </c>
       <c r="G3" s="0">
-        <v>0.57412789411699805</v>
+        <v>0.43415763013429043</v>
       </c>
       <c r="H3" s="0">
-        <v>19.925872105883002</v>
+        <v>20.06584236986571</v>
       </c>
       <c r="I3" s="0">
-        <v>-1.0741278941169981</v>
+        <v>-0.93415763013429043</v>
       </c>
       <c r="J3" s="0">
-        <v>1.0741278941169981</v>
+        <v>0.93415763013429043</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -581,28 +581,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>755.06500000000005</v>
+        <v>757.2885</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>23.488210382878023</v>
+        <v>23.684157858949135</v>
       </c>
       <c r="F4" s="0">
-        <v>-0.011789617121976903</v>
+        <v>0.18415785894913483</v>
       </c>
       <c r="G4" s="0">
-        <v>0.011789617121976903</v>
+        <v>0.18415785894913483</v>
       </c>
       <c r="H4" s="0">
-        <v>22.988210382878023</v>
+        <v>23.184157858949135</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.5117896171219769</v>
+        <v>-0.31584214105086517</v>
       </c>
       <c r="J4" s="0">
-        <v>0.5117896171219769</v>
+        <v>0.31584214105086517</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -625,28 +625,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.86080000000004</v>
+        <v>583.17809999999997</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>19.449636944758577</v>
+        <v>19.551174732647432</v>
       </c>
       <c r="F5" s="0">
-        <v>-1.5503630552414229</v>
+        <v>-1.4488252673525679</v>
       </c>
       <c r="G5" s="0">
-        <v>1.5503630552414229</v>
+        <v>1.4488252673525679</v>
       </c>
       <c r="H5" s="0">
-        <v>18.949636944758577</v>
+        <v>19.051174732647432</v>
       </c>
       <c r="I5" s="0">
-        <v>-2.0503630552414229</v>
+        <v>-1.9488252673525679</v>
       </c>
       <c r="J5" s="0">
-        <v>2.0503630552414229</v>
+        <v>1.9488252673525679</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -669,28 +669,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>634.26990000000001</v>
+        <v>633.10580000000004</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.018526222465859</v>
+        <v>20.949478344883453</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.48147377753414133</v>
+        <v>-0.55052165511654749</v>
       </c>
       <c r="G6" s="0">
-        <v>0.48147377753414133</v>
+        <v>0.55052165511654749</v>
       </c>
       <c r="H6" s="0">
-        <v>20.518526222465859</v>
+        <v>20.449478344883453</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.98147377753414133</v>
+        <v>-1.0505216551165475</v>
       </c>
       <c r="J6" s="0">
-        <v>0.98147377753414133</v>
+        <v>1.0505216551165475</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -713,28 +713,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>691.86599999999999</v>
+        <v>712.21130000000005</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.83282523541558</v>
+        <v>22.444870829059678</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.16717476458441993</v>
+        <v>0.44487082905967768</v>
       </c>
       <c r="G7" s="0">
-        <v>0.16717476458441993</v>
+        <v>0.44487082905967768</v>
       </c>
       <c r="H7" s="0">
-        <v>21.33282523541558</v>
+        <v>21.944870829059678</v>
       </c>
       <c r="I7" s="0">
-        <v>-0.66717476458441993</v>
+        <v>-0.055129170940322325</v>
       </c>
       <c r="J7" s="0">
-        <v>0.66717476458441993</v>
+        <v>0.055129170940322325</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -757,28 +757,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>763.82230000000004</v>
+        <v>765.37739999999997</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>23.707093340322256</v>
+        <v>24.133868899130867</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.2929066596777439</v>
+        <v>-0.86613110086913281</v>
       </c>
       <c r="G8" s="0">
-        <v>1.2929066596777439</v>
+        <v>0.86613110086913281</v>
       </c>
       <c r="H8" s="0">
-        <v>23.207093340322256</v>
+        <v>23.633868899130867</v>
       </c>
       <c r="I8" s="0">
-        <v>-1.7929066596777439</v>
+        <v>-1.3661311008691328</v>
       </c>
       <c r="J8" s="0">
-        <v>1.7929066596777439</v>
+        <v>1.3661311008691328</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -801,28 +801,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>612.55169999999998</v>
+        <v>584.5915</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>20.409082814247952</v>
+        <v>19.916334915415828</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.090917185752047658</v>
+        <v>-0.58366508458417243</v>
       </c>
       <c r="G9" s="0">
-        <v>0.090917185752047658</v>
+        <v>0.58366508458417243</v>
       </c>
       <c r="H9" s="0">
-        <v>19.909082814247952</v>
+        <v>19.416334915415828</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.59091718575204766</v>
+        <v>-1.0836650845841724</v>
       </c>
       <c r="J9" s="0">
-        <v>0.59091718575204766</v>
+        <v>1.0836650845841724</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -845,28 +845,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>647.83249999999998</v>
+        <v>648.39279999999997</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.46623154604734</v>
+        <v>21.404784808792407</v>
       </c>
       <c r="F10" s="0">
-        <v>0.46623154604733941</v>
+        <v>0.40478480879240664</v>
       </c>
       <c r="G10" s="0">
-        <v>0.46623154604733941</v>
+        <v>0.40478480879240664</v>
       </c>
       <c r="H10" s="0">
-        <v>20.96623154604734</v>
+        <v>20.904784808792407</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.033768453952660593</v>
+        <v>-0.095215191207593364</v>
       </c>
       <c r="J10" s="0">
-        <v>0.033768453952660593</v>
+        <v>0.095215191207593364</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -889,28 +889,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>468.75369999999998</v>
+        <v>466.6764</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>19.001344455442759</v>
+        <v>19.205849354398278</v>
       </c>
       <c r="F11" s="0">
-        <v>1.0013444554427586</v>
+        <v>1.2058493543982785</v>
       </c>
       <c r="G11" s="0">
-        <v>1.0013444554427586</v>
+        <v>1.2058493543982785</v>
       </c>
       <c r="H11" s="0">
-        <v>18.501344455442759</v>
+        <v>18.705849354398278</v>
       </c>
       <c r="I11" s="0">
-        <v>0.50134445544275863</v>
+        <v>0.70584935439827845</v>
       </c>
       <c r="J11" s="0">
-        <v>0.50134445544275863</v>
+        <v>0.70584935439827845</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -933,28 +933,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>745.02800000000002</v>
+        <v>747.66359999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>22.239280694413292</v>
+        <v>22.8134971911898</v>
       </c>
       <c r="F12" s="0">
-        <v>-2.7607193055867079</v>
+        <v>-2.1865028088102001</v>
       </c>
       <c r="G12" s="0">
-        <v>2.7607193055867079</v>
+        <v>2.1865028088102001</v>
       </c>
       <c r="H12" s="0">
-        <v>21.739280694413292</v>
+        <v>22.3134971911898</v>
       </c>
       <c r="I12" s="0">
-        <v>-3.2607193055867079</v>
+        <v>-2.6865028088102001</v>
       </c>
       <c r="J12" s="0">
-        <v>3.2607193055867079</v>
+        <v>2.6865028088102001</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -977,28 +977,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>674.10310000000004</v>
+        <v>659.65279999999996</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>21.506436506329617</v>
+        <v>20.797017017906693</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.99356349367038277</v>
+        <v>-1.7029829820933067</v>
       </c>
       <c r="G13" s="0">
-        <v>0.99356349367038277</v>
+        <v>1.7029829820933067</v>
       </c>
       <c r="H13" s="0">
-        <v>21.006436506329617</v>
+        <v>20.297017017906693</v>
       </c>
       <c r="I13" s="0">
-        <v>-1.4935634936703828</v>
+        <v>-2.2029829820933067</v>
       </c>
       <c r="J13" s="0">
-        <v>1.4935634936703828</v>
+        <v>2.2029829820933067</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1021,28 +1021,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>678.64329999999995</v>
+        <v>682.95950000000005</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.067602522881245</v>
+        <v>21.155001496223758</v>
       </c>
       <c r="F14" s="0">
-        <v>0.56760252288124491</v>
+        <v>0.65500149622375758</v>
       </c>
       <c r="G14" s="0">
-        <v>0.56760252288124491</v>
+        <v>0.65500149622375758</v>
       </c>
       <c r="H14" s="0">
-        <v>20.567602522881245</v>
+        <v>20.655001496223758</v>
       </c>
       <c r="I14" s="0">
-        <v>0.067602522881244909</v>
+        <v>0.15500149622375759</v>
       </c>
       <c r="J14" s="0">
-        <v>0.067602522881244909</v>
+        <v>0.15500149622375759</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1065,28 +1065,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>588.29200000000003</v>
+        <v>587.81489999999997</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>19.303306112168499</v>
+        <v>19.970135470205406</v>
       </c>
       <c r="F15" s="0">
-        <v>-0.19669388783150055</v>
+        <v>0.47013547020540614</v>
       </c>
       <c r="G15" s="0">
-        <v>0.19669388783150055</v>
+        <v>0.47013547020540614</v>
       </c>
       <c r="H15" s="0">
-        <v>18.803306112168499</v>
+        <v>19.470135470205406</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.69669388783150055</v>
+        <v>-0.029864529794593864</v>
       </c>
       <c r="J15" s="0">
-        <v>0.69669388783150055</v>
+        <v>0.029864529794593864</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>0</v>
@@ -1109,28 +1109,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>618.86260000000004</v>
+        <v>624.73410000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.515893519707134</v>
+        <v>21.56696386778129</v>
       </c>
       <c r="F16" s="0">
-        <v>2.0158935197071344</v>
+        <v>2.0669638677812898</v>
       </c>
       <c r="G16" s="0">
-        <v>2.0158935197071344</v>
+        <v>2.0669638677812898</v>
       </c>
       <c r="H16" s="0">
-        <v>21.015893519707134</v>
+        <v>21.06696386778129</v>
       </c>
       <c r="I16" s="0">
-        <v>1.5158935197071344</v>
+        <v>1.5669638677812898</v>
       </c>
       <c r="J16" s="0">
-        <v>1.5158935197071344</v>
+        <v>1.5669638677812898</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1153,28 +1153,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>557.87480000000005</v>
+        <v>564.40920000000006</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>19.43775344471856</v>
+        <v>19.506178126660455</v>
       </c>
       <c r="F17" s="0">
-        <v>0.93775344471855959</v>
+        <v>1.0061781266604548</v>
       </c>
       <c r="G17" s="0">
-        <v>0.93775344471855959</v>
+        <v>1.0061781266604548</v>
       </c>
       <c r="H17" s="0">
-        <v>18.93775344471856</v>
+        <v>19.006178126660455</v>
       </c>
       <c r="I17" s="0">
-        <v>0.43775344471855959</v>
+        <v>0.50617812666045481</v>
       </c>
       <c r="J17" s="0">
-        <v>0.43775344471855959</v>
+        <v>0.50617812666045481</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1197,28 +1197,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>734.02059999999995</v>
+        <v>736.66660000000002</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>22.174622123011655</v>
+        <v>22.556717145491433</v>
       </c>
       <c r="F18" s="0">
-        <v>-1.5753778769883446</v>
+        <v>-1.193282854508567</v>
       </c>
       <c r="G18" s="0">
-        <v>1.5753778769883446</v>
+        <v>1.193282854508567</v>
       </c>
       <c r="H18" s="0">
-        <v>21.674622123011655</v>
+        <v>22.056717145491433</v>
       </c>
       <c r="I18" s="0">
-        <v>-2.0753778769883446</v>
+        <v>-1.693282854508567</v>
       </c>
       <c r="J18" s="0">
-        <v>2.0753778769883446</v>
+        <v>1.693282854508567</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1241,28 +1241,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>674.8356</v>
+        <v>676.57719999999995</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>20.921687639306949</v>
+        <v>20.9099436664184</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.3283123606930509</v>
+        <v>-1.3400563335816003</v>
       </c>
       <c r="G19" s="0">
-        <v>1.3283123606930509</v>
+        <v>1.3400563335816003</v>
       </c>
       <c r="H19" s="0">
-        <v>20.421687639306949</v>
+        <v>20.4099436664184</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.8283123606930509</v>
+        <v>-1.8400563335816003</v>
       </c>
       <c r="J19" s="0">
-        <v>1.8283123606930509</v>
+        <v>1.8400563335816003</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1285,28 +1285,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>758.93589999999995</v>
+        <v>752.55830000000003</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>23.542005686399538</v>
+        <v>23.739646558212137</v>
       </c>
       <c r="F20" s="0">
-        <v>-1.9579943136004623</v>
+        <v>-1.7603534417878635</v>
       </c>
       <c r="G20" s="0">
-        <v>1.9579943136004623</v>
+        <v>1.7603534417878635</v>
       </c>
       <c r="H20" s="0">
-        <v>23.042005686399538</v>
+        <v>23.239646558212137</v>
       </c>
       <c r="I20" s="0">
-        <v>-2.4579943136004623</v>
+        <v>-2.2603534417878635</v>
       </c>
       <c r="J20" s="0">
-        <v>2.4579943136004623</v>
+        <v>2.2603534417878635</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1329,28 +1329,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>530.03160000000003</v>
+        <v>533.39049999999998</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>18.006907341121739</v>
+        <v>18.606474525321026</v>
       </c>
       <c r="F21" s="0">
-        <v>-4.4930926588782611</v>
+        <v>-3.8935254746789738</v>
       </c>
       <c r="G21" s="0">
-        <v>4.4930926588782611</v>
+        <v>3.8935254746789738</v>
       </c>
       <c r="H21" s="0">
-        <v>17.506907341121739</v>
+        <v>18.106474525321026</v>
       </c>
       <c r="I21" s="0">
-        <v>-4.9930926588782611</v>
+        <v>-4.3935254746789738</v>
       </c>
       <c r="J21" s="0">
-        <v>4.9930926588782611</v>
+        <v>4.3935254746789738</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1373,28 +1373,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>619.3691</v>
+        <v>617.12260000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>20.135000540300986</v>
+        <v>20.098397930624799</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.364999459699014</v>
+        <v>-1.4016020693752012</v>
       </c>
       <c r="G22" s="0">
-        <v>1.364999459699014</v>
+        <v>1.4016020693752012</v>
       </c>
       <c r="H22" s="0">
-        <v>19.635000540300986</v>
+        <v>19.598397930624799</v>
       </c>
       <c r="I22" s="0">
-        <v>-1.864999459699014</v>
+        <v>-1.9016020693752012</v>
       </c>
       <c r="J22" s="0">
-        <v>1.864999459699014</v>
+        <v>1.9016020693752012</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1417,28 +1417,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>681.04340000000002</v>
+        <v>669.44370000000004</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.867104973931106</v>
+        <v>21.630517833267437</v>
       </c>
       <c r="F23" s="0">
-        <v>1.8671049739311059</v>
+        <v>1.6305178332674366</v>
       </c>
       <c r="G23" s="0">
-        <v>1.8671049739311059</v>
+        <v>1.6305178332674366</v>
       </c>
       <c r="H23" s="0">
-        <v>21.367104973931106</v>
+        <v>21.130517833267437</v>
       </c>
       <c r="I23" s="0">
-        <v>1.3671049739311059</v>
+        <v>1.1305178332674366</v>
       </c>
       <c r="J23" s="0">
-        <v>1.3671049739311059</v>
+        <v>1.1305178332674366</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1461,28 +1461,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>585.4384</v>
+        <v>584.04089999999997</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>19.799481298368136</v>
+        <v>19.732442620942173</v>
       </c>
       <c r="F24" s="0">
-        <v>0.29948129836813564</v>
+        <v>0.23244262094217305</v>
       </c>
       <c r="G24" s="0">
-        <v>0.29948129836813564</v>
+        <v>0.23244262094217305</v>
       </c>
       <c r="H24" s="0">
-        <v>19.299481298368136</v>
+        <v>19.232442620942173</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.20051870163186436</v>
+        <v>-0.26755737905782695</v>
       </c>
       <c r="J24" s="0">
-        <v>0.20051870163186436</v>
+        <v>0.26755737905782695</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>0</v>
@@ -1505,28 +1505,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>581.173</v>
+        <v>583.09950000000003</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>19.830382849733255</v>
+        <v>19.804103529060985</v>
       </c>
       <c r="F25" s="0">
-        <v>1.3303828497332546</v>
+        <v>1.3041035290609848</v>
       </c>
       <c r="G25" s="0">
-        <v>1.3303828497332546</v>
+        <v>1.3041035290609848</v>
       </c>
       <c r="H25" s="0">
-        <v>19.330382849733255</v>
+        <v>19.304103529060985</v>
       </c>
       <c r="I25" s="0">
-        <v>0.8303828497332546</v>
+        <v>0.80410352906098481</v>
       </c>
       <c r="J25" s="0">
-        <v>0.8303828497332546</v>
+        <v>0.80410352906098481</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1549,28 +1549,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>692.99239999999998</v>
+        <v>694.29290000000003</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>22.000671636359716</v>
+        <v>21.855096841537648</v>
       </c>
       <c r="F26" s="0">
-        <v>0.75067163635971568</v>
+        <v>0.60509684153764809</v>
       </c>
       <c r="G26" s="0">
-        <v>0.75067163635971568</v>
+        <v>0.60509684153764809</v>
       </c>
       <c r="H26" s="0">
-        <v>21.500671636359716</v>
+        <v>21.355096841537648</v>
       </c>
       <c r="I26" s="0">
-        <v>0.25067163635971568</v>
+        <v>0.10509684153764809</v>
       </c>
       <c r="J26" s="0">
-        <v>0.25067163635971568</v>
+        <v>0.10509684153764809</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>1</v>
@@ -1593,28 +1593,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>643.06439999999998</v>
+        <v>645.69730000000004</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>20.765178518281285</v>
+        <v>20.778326810891606</v>
       </c>
       <c r="F27" s="0">
-        <v>1.5151785182812851</v>
+        <v>1.5283268108916062</v>
       </c>
       <c r="G27" s="0">
-        <v>1.5151785182812851</v>
+        <v>1.5283268108916062</v>
       </c>
       <c r="H27" s="0">
-        <v>20.265178518281285</v>
+        <v>20.278326810891606</v>
       </c>
       <c r="I27" s="0">
-        <v>1.0151785182812851</v>
+        <v>1.0283268108916062</v>
       </c>
       <c r="J27" s="0">
-        <v>1.0151785182812851</v>
+        <v>1.0283268108916062</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1637,28 +1637,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>679.27729999999997</v>
+        <v>704.87890000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.224704528388006</v>
+        <v>21.895304994701583</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.52529547161199375</v>
+        <v>0.14530499470158276</v>
       </c>
       <c r="G28" s="0">
-        <v>0.52529547161199375</v>
+        <v>0.14530499470158276</v>
       </c>
       <c r="H28" s="0">
-        <v>20.724704528388006</v>
+        <v>21.395304994701583</v>
       </c>
       <c r="I28" s="0">
-        <v>-1.0252954716119938</v>
+        <v>-0.35469500529841724</v>
       </c>
       <c r="J28" s="0">
-        <v>1.0252954716119938</v>
+        <v>0.35469500529841724</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1681,28 +1681,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>531.55600000000004</v>
+        <v>527.93060000000003</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>19.121228006223184</v>
+        <v>19.119057926290459</v>
       </c>
       <c r="F29" s="0">
-        <v>-1.6287719937768159</v>
+        <v>-1.6309420737095408</v>
       </c>
       <c r="G29" s="0">
-        <v>1.6287719937768159</v>
+        <v>1.6309420737095408</v>
       </c>
       <c r="H29" s="0">
-        <v>18.621228006223184</v>
+        <v>18.619057926290459</v>
       </c>
       <c r="I29" s="0">
-        <v>-2.1287719937768159</v>
+        <v>-2.1309420737095408</v>
       </c>
       <c r="J29" s="0">
-        <v>2.1287719937768159</v>
+        <v>2.1309420737095408</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1725,28 +1725,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>685.61059999999998</v>
+        <v>688.96929999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>22.455521879021603</v>
+        <v>22.503996589006434</v>
       </c>
       <c r="F30" s="0">
-        <v>0.95552187902160313</v>
+        <v>1.0039965890064337</v>
       </c>
       <c r="G30" s="0">
-        <v>0.95552187902160313</v>
+        <v>1.0039965890064337</v>
       </c>
       <c r="H30" s="0">
-        <v>21.955521879021603</v>
+        <v>22.003996589006434</v>
       </c>
       <c r="I30" s="0">
-        <v>0.45552187902160313</v>
+        <v>0.50399658900643374</v>
       </c>
       <c r="J30" s="0">
-        <v>0.45552187902160313</v>
+        <v>0.50399658900643374</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>1</v>
@@ -1769,28 +1769,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>683.32539999999995</v>
+        <v>687.38679999999999</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>22.859851809126589</v>
+        <v>22.939003781833691</v>
       </c>
       <c r="F31" s="0">
-        <v>3.3598518091265888</v>
+        <v>3.4390037818336907</v>
       </c>
       <c r="G31" s="0">
-        <v>3.3598518091265888</v>
+        <v>3.4390037818336907</v>
       </c>
       <c r="H31" s="0">
-        <v>22.359851809126589</v>
+        <v>22.439003781833691</v>
       </c>
       <c r="I31" s="0">
-        <v>2.8598518091265888</v>
+        <v>2.9390037818336907</v>
       </c>
       <c r="J31" s="0">
-        <v>2.8598518091265888</v>
+        <v>2.9390037818336907</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1813,28 +1813,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>669.30840000000001</v>
+        <v>664.20730000000003</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>22.536664890691025</v>
+        <v>22.371727367765342</v>
       </c>
       <c r="F32" s="0">
-        <v>3.036664890691025</v>
+        <v>2.8717273677653417</v>
       </c>
       <c r="G32" s="0">
-        <v>3.036664890691025</v>
+        <v>2.8717273677653417</v>
       </c>
       <c r="H32" s="0">
-        <v>22.036664890691025</v>
+        <v>21.871727367765342</v>
       </c>
       <c r="I32" s="0">
-        <v>2.536664890691025</v>
+        <v>2.3717273677653417</v>
       </c>
       <c r="J32" s="0">
-        <v>2.536664890691025</v>
+        <v>2.3717273677653417</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1857,28 +1857,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>712.56219999999996</v>
+        <v>700.82140000000004</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.431331356548817</v>
+        <v>21.237104912271434</v>
       </c>
       <c r="F33" s="0">
-        <v>0.43133135654881727</v>
+        <v>0.23710491227143393</v>
       </c>
       <c r="G33" s="0">
-        <v>0.43133135654881727</v>
+        <v>0.23710491227143393</v>
       </c>
       <c r="H33" s="0">
-        <v>20.931331356548817</v>
+        <v>20.737104912271434</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.068668643451182732</v>
+        <v>-0.26289508772856607</v>
       </c>
       <c r="J33" s="0">
-        <v>0.068668643451182732</v>
+        <v>0.26289508772856607</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>0</v>
@@ -1901,28 +1901,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.39670000000001</v>
+        <v>604.36569999999995</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>19.934442744989561</v>
+        <v>20.135432948567601</v>
       </c>
       <c r="F34" s="0">
-        <v>-0.31555725501043952</v>
+        <v>-0.11456705143239887</v>
       </c>
       <c r="G34" s="0">
-        <v>0.31555725501043952</v>
+        <v>0.11456705143239887</v>
       </c>
       <c r="H34" s="0">
-        <v>19.434442744989561</v>
+        <v>19.635432948567601</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.81555725501043952</v>
+        <v>-0.61456705143239887</v>
       </c>
       <c r="J34" s="0">
-        <v>0.81555725501043952</v>
+        <v>0.61456705143239887</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>0</v>
@@ -1945,28 +1945,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>622.68050000000005</v>
+        <v>621.61170000000004</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>20.274307969046678</v>
+        <v>20.17190669617057</v>
       </c>
       <c r="F35" s="0">
-        <v>-1.2256920309533221</v>
+        <v>-1.32809330382943</v>
       </c>
       <c r="G35" s="0">
-        <v>1.2256920309533221</v>
+        <v>1.32809330382943</v>
       </c>
       <c r="H35" s="0">
-        <v>19.774307969046678</v>
+        <v>19.67190669617057</v>
       </c>
       <c r="I35" s="0">
-        <v>-1.7256920309533221</v>
+        <v>-1.82809330382943</v>
       </c>
       <c r="J35" s="0">
-        <v>1.7256920309533221</v>
+        <v>1.82809330382943</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1989,31 +1989,31 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>601.95100000000002</v>
+        <v>597.18910000000005</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>20.006615706764233</v>
+        <v>19.896535726488967</v>
       </c>
       <c r="F36" s="0">
-        <v>0.50661570676423295</v>
+        <v>0.39653572648896685</v>
       </c>
       <c r="G36" s="0">
-        <v>0.50661570676423295</v>
+        <v>0.39653572648896685</v>
       </c>
       <c r="H36" s="0">
-        <v>19.506615706764233</v>
+        <v>19.396535726488967</v>
       </c>
       <c r="I36" s="0">
-        <v>0.0066157067642329537</v>
+        <v>-0.10346427351103316</v>
       </c>
       <c r="J36" s="0">
-        <v>0.0066157067642329537</v>
+        <v>0.10346427351103316</v>
       </c>
       <c r="K36" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="0">
         <v>1</v>
@@ -2033,28 +2033,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>726.80799999999999</v>
+        <v>738.8483</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>22.477249334699906</v>
+        <v>22.81063005613677</v>
       </c>
       <c r="F37" s="0">
-        <v>-2.5227506653000944</v>
+        <v>-2.1893699438632304</v>
       </c>
       <c r="G37" s="0">
-        <v>2.5227506653000944</v>
+        <v>2.1893699438632304</v>
       </c>
       <c r="H37" s="0">
-        <v>21.977249334699906</v>
+        <v>22.31063005613677</v>
       </c>
       <c r="I37" s="0">
-        <v>-3.0227506653000944</v>
+        <v>-2.6893699438632304</v>
       </c>
       <c r="J37" s="0">
-        <v>3.0227506653000944</v>
+        <v>2.6893699438632304</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2077,28 +2077,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>599.73789999999997</v>
+        <v>595.78989999999999</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>19.828035886203477</v>
+        <v>19.781371716741823</v>
       </c>
       <c r="F38" s="0">
-        <v>0.82803588620347668</v>
+        <v>0.78137171674182326</v>
       </c>
       <c r="G38" s="0">
-        <v>0.82803588620347668</v>
+        <v>0.78137171674182326</v>
       </c>
       <c r="H38" s="0">
-        <v>19.328035886203477</v>
+        <v>19.281371716741823</v>
       </c>
       <c r="I38" s="0">
-        <v>0.32803588620347668</v>
+        <v>0.28137171674182326</v>
       </c>
       <c r="J38" s="0">
-        <v>0.32803588620347668</v>
+        <v>0.28137171674182326</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2121,28 +2121,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>700.04589999999996</v>
+        <v>698.92719999999997</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>21.528516750683217</v>
+        <v>21.250065342791416</v>
       </c>
       <c r="F39" s="0">
-        <v>2.5285167506832167</v>
+        <v>2.2500653427914159</v>
       </c>
       <c r="G39" s="0">
-        <v>2.5285167506832167</v>
+        <v>2.2500653427914159</v>
       </c>
       <c r="H39" s="0">
-        <v>21.028516750683217</v>
+        <v>20.750065342791416</v>
       </c>
       <c r="I39" s="0">
-        <v>2.0285167506832167</v>
+        <v>1.7500653427914159</v>
       </c>
       <c r="J39" s="0">
-        <v>2.0285167506832167</v>
+        <v>1.7500653427914159</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2165,28 +2165,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>776.98199999999997</v>
+        <v>762.38530000000003</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>22.990680354724027</v>
+        <v>22.706451769274963</v>
       </c>
       <c r="F40" s="0">
-        <v>1.9906803547240273</v>
+        <v>1.7064517692749632</v>
       </c>
       <c r="G40" s="0">
-        <v>1.9906803547240273</v>
+        <v>1.7064517692749632</v>
       </c>
       <c r="H40" s="0">
-        <v>22.490680354724027</v>
+        <v>22.206451769274963</v>
       </c>
       <c r="I40" s="0">
-        <v>1.4906803547240273</v>
+        <v>1.2064517692749632</v>
       </c>
       <c r="J40" s="0">
-        <v>1.4906803547240273</v>
+        <v>1.2064517692749632</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>1</v>
@@ -2209,28 +2209,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>673.32410000000004</v>
+        <v>672.51900000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>20.977325833942544</v>
+        <v>20.949202053069577</v>
       </c>
       <c r="F41" s="0">
-        <v>0.47732583394254391</v>
+        <v>0.44920205306957683</v>
       </c>
       <c r="G41" s="0">
-        <v>0.47732583394254391</v>
+        <v>0.44920205306957683</v>
       </c>
       <c r="H41" s="0">
-        <v>20.477325833942544</v>
+        <v>20.449202053069577</v>
       </c>
       <c r="I41" s="0">
-        <v>-0.022674166057456091</v>
+        <v>-0.050797946930423166</v>
       </c>
       <c r="J41" s="0">
-        <v>0.022674166057456091</v>
+        <v>0.050797946930423166</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>0</v>
@@ -2253,28 +2253,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>526.36469999999997</v>
+        <v>523.23350000000005</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>19.30938198748332</v>
+        <v>19.199301584718207</v>
       </c>
       <c r="F42" s="0">
-        <v>0.059381987483320131</v>
+        <v>-0.05069841528179353</v>
       </c>
       <c r="G42" s="0">
-        <v>0.059381987483320131</v>
+        <v>0.05069841528179353</v>
       </c>
       <c r="H42" s="0">
-        <v>18.80938198748332</v>
+        <v>18.699301584718207</v>
       </c>
       <c r="I42" s="0">
-        <v>-0.44061801251667987</v>
+        <v>-0.55069841528179353</v>
       </c>
       <c r="J42" s="0">
-        <v>0.44061801251667987</v>
+        <v>0.55069841528179353</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>0</v>
@@ -2297,28 +2297,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>586.85530000000006</v>
+        <v>585.99260000000004</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>19.524304762220524</v>
+        <v>19.580426459294554</v>
       </c>
       <c r="F43" s="0">
-        <v>-0.47569523777947609</v>
+        <v>-0.41957354070544639</v>
       </c>
       <c r="G43" s="0">
-        <v>0.47569523777947609</v>
+        <v>0.41957354070544639</v>
       </c>
       <c r="H43" s="0">
-        <v>19.024304762220524</v>
+        <v>19.080426459294554</v>
       </c>
       <c r="I43" s="0">
-        <v>-0.97569523777947609</v>
+        <v>-0.91957354070544639</v>
       </c>
       <c r="J43" s="0">
-        <v>0.97569523777947609</v>
+        <v>0.91957354070544639</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>0</v>
@@ -2341,28 +2341,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>663.21749999999997</v>
+        <v>661.50829999999996</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>21.242274607514428</v>
+        <v>20.718085880536592</v>
       </c>
       <c r="F44" s="0">
-        <v>1.2422746075144282</v>
+        <v>0.7180858805365915</v>
       </c>
       <c r="G44" s="0">
-        <v>1.2422746075144282</v>
+        <v>0.7180858805365915</v>
       </c>
       <c r="H44" s="0">
-        <v>20.742274607514428</v>
+        <v>20.218085880536592</v>
       </c>
       <c r="I44" s="0">
-        <v>0.7422746075144282</v>
+        <v>0.2180858805365915</v>
       </c>
       <c r="J44" s="0">
-        <v>0.7422746075144282</v>
+        <v>0.2180858805365915</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2385,28 +2385,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>582.90459999999996</v>
+        <v>579.78219999999999</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>19.821742497353711</v>
+        <v>19.758521887655551</v>
       </c>
       <c r="F45" s="0">
-        <v>-0.17825750264628937</v>
+        <v>-0.24147811234444916</v>
       </c>
       <c r="G45" s="0">
-        <v>0.17825750264628937</v>
+        <v>0.24147811234444916</v>
       </c>
       <c r="H45" s="0">
-        <v>19.321742497353711</v>
+        <v>19.258521887655551</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.67825750264628937</v>
+        <v>-0.74147811234444916</v>
       </c>
       <c r="J45" s="0">
-        <v>0.67825750264628937</v>
+        <v>0.74147811234444916</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>0</v>
@@ -2429,28 +2429,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>732.64890000000003</v>
+        <v>725.4751</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>22.543041164304</v>
+        <v>22.645833202565136</v>
       </c>
       <c r="F46" s="0">
-        <v>0.54304116430400029</v>
+        <v>0.64583320256513588</v>
       </c>
       <c r="G46" s="0">
-        <v>0.54304116430400029</v>
+        <v>0.64583320256513588</v>
       </c>
       <c r="H46" s="0">
-        <v>22.043041164304</v>
+        <v>22.145833202565136</v>
       </c>
       <c r="I46" s="0">
-        <v>0.04304116430400029</v>
+        <v>0.14583320256513588</v>
       </c>
       <c r="J46" s="0">
-        <v>0.04304116430400029</v>
+        <v>0.14583320256513588</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>1</v>
@@ -2473,28 +2473,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>704.21619999999996</v>
+        <v>700.72990000000004</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>22.20802713167609</v>
+        <v>22.054865358652641</v>
       </c>
       <c r="F47" s="0">
-        <v>0.20802713167608999</v>
+        <v>0.054865358652641305</v>
       </c>
       <c r="G47" s="0">
-        <v>0.20802713167608999</v>
+        <v>0.054865358652641305</v>
       </c>
       <c r="H47" s="0">
-        <v>21.70802713167609</v>
+        <v>21.554865358652641</v>
       </c>
       <c r="I47" s="0">
-        <v>-0.29197286832391001</v>
+        <v>-0.4451346413473587</v>
       </c>
       <c r="J47" s="0">
-        <v>0.29197286832391001</v>
+        <v>0.4451346413473587</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2517,28 +2517,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>707.67989999999998</v>
+        <v>697.40779999999995</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.790102945247494</v>
+        <v>21.577509037585653</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.2098970547525063</v>
+        <v>-1.4224909624143471</v>
       </c>
       <c r="G48" s="0">
-        <v>1.2098970547525063</v>
+        <v>1.4224909624143471</v>
       </c>
       <c r="H48" s="0">
-        <v>21.290102945247494</v>
+        <v>21.077509037585653</v>
       </c>
       <c r="I48" s="0">
-        <v>-1.7098970547525063</v>
+        <v>-1.9224909624143471</v>
       </c>
       <c r="J48" s="0">
-        <v>1.7098970547525063</v>
+        <v>1.9224909624143471</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2561,28 +2561,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>666.81700000000001</v>
+        <v>664.56500000000005</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>20.856283137567218</v>
+        <v>20.749377562348499</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.89371686243278248</v>
+        <v>-1.0006224376515007</v>
       </c>
       <c r="G49" s="0">
-        <v>0.89371686243278248</v>
+        <v>1.0006224376515007</v>
       </c>
       <c r="H49" s="0">
-        <v>20.356283137567218</v>
+        <v>20.249377562348499</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.3937168624327825</v>
+        <v>-1.5006224376515007</v>
       </c>
       <c r="J49" s="0">
-        <v>1.3937168624327825</v>
+        <v>1.5006224376515007</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2605,28 +2605,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>688.77390000000003</v>
+        <v>689.15930000000003</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.42663746000801</v>
+        <v>21.461506664770017</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.073362539991990161</v>
+        <v>-0.038493335229983217</v>
       </c>
       <c r="G50" s="0">
-        <v>0.073362539991990161</v>
+        <v>0.038493335229983217</v>
       </c>
       <c r="H50" s="0">
-        <v>20.92663746000801</v>
+        <v>20.961506664770017</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.57336253999199016</v>
+        <v>-0.53849333522998322</v>
       </c>
       <c r="J50" s="0">
-        <v>0.57336253999199016</v>
+        <v>0.53849333522998322</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2649,28 +2649,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>615.82560000000001</v>
+        <v>610.64480000000003</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>20.100556864549521</v>
+        <v>19.989904368046005</v>
       </c>
       <c r="F51" s="0">
-        <v>0.90055686454952166</v>
+        <v>0.78990436804600606</v>
       </c>
       <c r="G51" s="0">
-        <v>0.90055686454952166</v>
+        <v>0.78990436804600606</v>
       </c>
       <c r="H51" s="0">
-        <v>19.600556864549521</v>
+        <v>19.489904368046005</v>
       </c>
       <c r="I51" s="0">
-        <v>0.40055686454952166</v>
+        <v>0.28990436804600606</v>
       </c>
       <c r="J51" s="0">
-        <v>0.40055686454952166</v>
+        <v>0.28990436804600606</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2693,28 +2693,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>568.91740000000004</v>
+        <v>576.71630000000005</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>19.599965195223376</v>
+        <v>19.676698555531729</v>
       </c>
       <c r="F52" s="0">
-        <v>2.0999651952233762</v>
+        <v>2.1766985555317291</v>
       </c>
       <c r="G52" s="0">
-        <v>2.0999651952233762</v>
+        <v>2.1766985555317291</v>
       </c>
       <c r="H52" s="0">
-        <v>19.099965195223376</v>
+        <v>19.176698555531729</v>
       </c>
       <c r="I52" s="0">
-        <v>1.5999651952233762</v>
+        <v>1.6766985555317291</v>
       </c>
       <c r="J52" s="0">
-        <v>1.5999651952233762</v>
+        <v>1.6766985555317291</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2737,28 +2737,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>594.03499999999997</v>
+        <v>598.05470000000003</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>19.950104077343926</v>
+        <v>19.967755699767693</v>
       </c>
       <c r="F53" s="0">
-        <v>1.5501040773439279</v>
+        <v>1.5677556997676945</v>
       </c>
       <c r="G53" s="0">
-        <v>1.5501040773439279</v>
+        <v>1.5677556997676945</v>
       </c>
       <c r="H53" s="0">
-        <v>19.450104077343926</v>
+        <v>19.467755699767693</v>
       </c>
       <c r="I53" s="0">
-        <v>1.0501040773439279</v>
+        <v>1.0677556997676945</v>
       </c>
       <c r="J53" s="0">
-        <v>1.0501040773439279</v>
+        <v>1.0677556997676945</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2781,31 +2781,31 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>566.51940000000002</v>
+        <v>573.06939999999997</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>19.467938981154323</v>
+        <v>19.575673059200288</v>
       </c>
       <c r="F54" s="0">
-        <v>0.46793898115432242</v>
+        <v>0.57567305920028744</v>
       </c>
       <c r="G54" s="0">
-        <v>0.46793898115432242</v>
+        <v>0.57567305920028744</v>
       </c>
       <c r="H54" s="0">
-        <v>18.967938981154323</v>
+        <v>19.075673059200288</v>
       </c>
       <c r="I54" s="0">
-        <v>-0.03206101884567758</v>
+        <v>0.07567305920028744</v>
       </c>
       <c r="J54" s="0">
-        <v>0.03206101884567758</v>
+        <v>0.07567305920028744</v>
       </c>
       <c r="K54" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="0">
         <v>5</v>
@@ -2825,28 +2825,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>614.26739999999995</v>
+        <v>610.65390000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>20.186651075991755</v>
+        <v>20.074569395536933</v>
       </c>
       <c r="F55" s="0">
-        <v>0.68665107599175457</v>
+        <v>0.57456939553693331</v>
       </c>
       <c r="G55" s="0">
-        <v>0.68665107599175457</v>
+        <v>0.57456939553693331</v>
       </c>
       <c r="H55" s="0">
-        <v>19.686651075991755</v>
+        <v>19.574569395536933</v>
       </c>
       <c r="I55" s="0">
-        <v>0.18665107599175457</v>
+        <v>0.074569395536933314</v>
       </c>
       <c r="J55" s="0">
-        <v>0.18665107599175457</v>
+        <v>0.074569395536933314</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2869,28 +2869,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>717.47789999999998</v>
+        <v>701.03470000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>22.689381446539201</v>
+        <v>22.358083499731155</v>
       </c>
       <c r="F56" s="0">
-        <v>2.1893814465392012</v>
+        <v>1.8580834997311548</v>
       </c>
       <c r="G56" s="0">
-        <v>2.1893814465392012</v>
+        <v>1.8580834997311548</v>
       </c>
       <c r="H56" s="0">
-        <v>22.189381446539201</v>
+        <v>21.858083499731155</v>
       </c>
       <c r="I56" s="0">
-        <v>1.6893814465392012</v>
+        <v>1.3580834997311548</v>
       </c>
       <c r="J56" s="0">
-        <v>1.6893814465392012</v>
+        <v>1.3580834997311548</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>1</v>
@@ -2913,28 +2913,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>656.12369999999999</v>
+        <v>647.98350000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>21.14239262800848</v>
+        <v>20.851460709779047</v>
       </c>
       <c r="F57" s="0">
-        <v>0.14239262800847996</v>
+        <v>-0.14853929022095258</v>
       </c>
       <c r="G57" s="0">
-        <v>0.14239262800847996</v>
+        <v>0.14853929022095258</v>
       </c>
       <c r="H57" s="0">
-        <v>20.64239262800848</v>
+        <v>20.351460709779047</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.35760737199152004</v>
+        <v>-0.64853929022095258</v>
       </c>
       <c r="J57" s="0">
-        <v>0.35760737199152004</v>
+        <v>0.64853929022095258</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2957,28 +2957,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>713.17060000000004</v>
+        <v>713.38980000000004</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>21.958003930618059</v>
+        <v>22.008553556303056</v>
       </c>
       <c r="F58" s="0">
-        <v>-1.5419960693819412</v>
+        <v>-1.4914464436969439</v>
       </c>
       <c r="G58" s="0">
-        <v>1.5419960693819412</v>
+        <v>1.4914464436969439</v>
       </c>
       <c r="H58" s="0">
-        <v>21.458003930618059</v>
+        <v>21.508553556303056</v>
       </c>
       <c r="I58" s="0">
-        <v>-2.0419960693819412</v>
+        <v>-1.9914464436969439</v>
       </c>
       <c r="J58" s="0">
-        <v>2.0419960693819412</v>
+        <v>1.9914464436969439</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -3001,28 +3001,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>675.12120000000004</v>
+        <v>672.01580000000001</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.809691270268896</v>
+        <v>21.677573980642581</v>
       </c>
       <c r="F59" s="0">
-        <v>1.3096912702688961</v>
+        <v>1.1775739806425811</v>
       </c>
       <c r="G59" s="0">
-        <v>1.3096912702688961</v>
+        <v>1.1775739806425811</v>
       </c>
       <c r="H59" s="0">
-        <v>21.309691270268896</v>
+        <v>21.177573980642581</v>
       </c>
       <c r="I59" s="0">
-        <v>0.80969127026889609</v>
+        <v>0.67757398064258112</v>
       </c>
       <c r="J59" s="0">
-        <v>0.80969127026889609</v>
+        <v>0.67757398064258112</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3045,28 +3045,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>689.68129999999997</v>
+        <v>697.428</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.575481779946344</v>
+        <v>21.735155480117353</v>
       </c>
       <c r="F60" s="0">
-        <v>0.075481779946343863</v>
+        <v>0.23515548011735277</v>
       </c>
       <c r="G60" s="0">
-        <v>0.075481779946343863</v>
+        <v>0.23515548011735277</v>
       </c>
       <c r="H60" s="0">
-        <v>21.075481779946344</v>
+        <v>21.235155480117353</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.42451822005365614</v>
+        <v>-0.26484451988264723</v>
       </c>
       <c r="J60" s="0">
-        <v>0.42451822005365614</v>
+        <v>0.26484451988264723</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3089,28 +3089,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>646.9873</v>
+        <v>648.5258</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>20.5296578299854</v>
+        <v>20.551887067955111</v>
       </c>
       <c r="F61" s="0">
-        <v>0.52965782998539979</v>
+        <v>0.55188706795511067</v>
       </c>
       <c r="G61" s="0">
-        <v>0.52965782998539979</v>
+        <v>0.55188706795511067</v>
       </c>
       <c r="H61" s="0">
-        <v>20.0296578299854</v>
+        <v>20.051887067955111</v>
       </c>
       <c r="I61" s="0">
-        <v>0.029657829985399786</v>
+        <v>0.051887067955110666</v>
       </c>
       <c r="J61" s="0">
-        <v>0.029657829985399786</v>
+        <v>0.051887067955110666</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3133,28 +3133,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>680.14350000000002</v>
+        <v>690.99220000000003</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.173560295212376</v>
+        <v>21.386149538986462</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.8264397047876244</v>
+        <v>-1.6138504610135378</v>
       </c>
       <c r="G62" s="0">
-        <v>1.8264397047876244</v>
+        <v>1.6138504610135378</v>
       </c>
       <c r="H62" s="0">
-        <v>20.673560295212376</v>
+        <v>20.886149538986462</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.3264397047876244</v>
+        <v>-2.1138504610135378</v>
       </c>
       <c r="J62" s="0">
-        <v>2.3264397047876244</v>
+        <v>2.1138504610135378</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3177,28 +3177,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>675.0444</v>
+        <v>674.3954</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.587177224707034</v>
+        <v>21.316840977743158</v>
       </c>
       <c r="F63" s="0">
-        <v>0.087177224707033929</v>
+        <v>-0.18315902225684155</v>
       </c>
       <c r="G63" s="0">
-        <v>0.087177224707033929</v>
+        <v>0.18315902225684155</v>
       </c>
       <c r="H63" s="0">
-        <v>21.087177224707034</v>
+        <v>20.816840977743158</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.41282277529296607</v>
+        <v>-0.68315902225684155</v>
       </c>
       <c r="J63" s="0">
-        <v>0.41282277529296607</v>
+        <v>0.68315902225684155</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3221,28 +3221,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>638.85119999999995</v>
+        <v>643.54809999999998</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.517922328123262</v>
+        <v>20.545065486971396</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.9820776718767377</v>
+        <v>-1.9549345130286042</v>
       </c>
       <c r="G64" s="0">
-        <v>1.9820776718767377</v>
+        <v>1.9549345130286042</v>
       </c>
       <c r="H64" s="0">
-        <v>20.017922328123262</v>
+        <v>20.045065486971396</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.4820776718767377</v>
+        <v>-2.4549345130286042</v>
       </c>
       <c r="J64" s="0">
-        <v>2.4820776718767377</v>
+        <v>2.4549345130286042</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3265,28 +3265,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>595.31380000000001</v>
+        <v>597.84789999999998</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>19.94440481022745</v>
+        <v>19.974965560830739</v>
       </c>
       <c r="F65" s="0">
-        <v>0.69440481022745004</v>
+        <v>0.72496556083073927</v>
       </c>
       <c r="G65" s="0">
-        <v>0.69440481022745004</v>
+        <v>0.72496556083073927</v>
       </c>
       <c r="H65" s="0">
-        <v>19.44440481022745</v>
+        <v>19.474965560830739</v>
       </c>
       <c r="I65" s="0">
-        <v>0.19440481022745004</v>
+        <v>0.22496556083073926</v>
       </c>
       <c r="J65" s="0">
-        <v>0.19440481022745004</v>
+        <v>0.22496556083073926</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3309,28 +3309,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>698.0498</v>
+        <v>710.17049999999995</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.447023574722206</v>
+        <v>21.733443208130652</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.0529764252777945</v>
+        <v>-1.7665567918693483</v>
       </c>
       <c r="G66" s="0">
-        <v>2.0529764252777945</v>
+        <v>1.7665567918693483</v>
       </c>
       <c r="H66" s="0">
-        <v>20.947023574722206</v>
+        <v>21.233443208130652</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.5529764252777945</v>
+        <v>-2.2665567918693483</v>
       </c>
       <c r="J66" s="0">
-        <v>2.5529764252777945</v>
+        <v>2.2665567918693483</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3353,28 +3353,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>634.08339999999998</v>
+        <v>639.05380000000002</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>20.351278719564263</v>
+        <v>20.344513873948795</v>
       </c>
       <c r="F67" s="0">
-        <v>-1.148721280435737</v>
+        <v>-1.1554861260512048</v>
       </c>
       <c r="G67" s="0">
-        <v>1.148721280435737</v>
+        <v>1.1554861260512048</v>
       </c>
       <c r="H67" s="0">
-        <v>19.851278719564263</v>
+        <v>19.844513873948795</v>
       </c>
       <c r="I67" s="0">
-        <v>-1.648721280435737</v>
+        <v>-1.6554861260512048</v>
       </c>
       <c r="J67" s="0">
-        <v>1.648721280435737</v>
+        <v>1.6554861260512048</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3397,28 +3397,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>578.7296</v>
+        <v>581.15859999999998</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>20.028191805653481</v>
+        <v>19.943868468797351</v>
       </c>
       <c r="F68" s="0">
-        <v>1.0281918056534813</v>
+        <v>0.94386846879735131</v>
       </c>
       <c r="G68" s="0">
-        <v>1.0281918056534813</v>
+        <v>0.94386846879735131</v>
       </c>
       <c r="H68" s="0">
-        <v>19.528191805653481</v>
+        <v>19.443868468797351</v>
       </c>
       <c r="I68" s="0">
-        <v>0.52819180565348134</v>
+        <v>0.44386846879735131</v>
       </c>
       <c r="J68" s="0">
-        <v>0.52819180565348134</v>
+        <v>0.44386846879735131</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3479,16 +3479,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.1619999999999999</v>
+        <v>1.117</v>
       </c>
       <c r="C2" s="0">
-        <v>1.4750000000000001</v>
+        <v>1.3999999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>0.32700000000000001</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.0070000000000000001</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3498,22 +3498,22 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C3" s="0">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="D3" s="0">
-        <v>0</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="E3" s="0">
-        <v>0</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="F3" s="0">
         <v>0</v>
       </c>
       <c r="G3" s="0">
-        <v>0</v>
+        <v>0.59999999999999998</v>
       </c>
     </row>
     <row r="4">
@@ -3532,18 +3532,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.1930000000000001</v>
+        <v>1.135</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.50700000000000001</v>
+        <v>-0.49199999999999999</v>
       </c>
       <c r="F5" s="0">
         <v>52.200000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>38.799999999999997</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="6">
@@ -3551,16 +3551,16 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.121</v>
+        <v>1.109</v>
       </c>
       <c r="C6" s="0">
-        <v>1.417</v>
+        <v>1.389</v>
       </c>
       <c r="D6" s="0">
-        <v>0.374</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.0089999999999999993</v>
+        <v>-0.01</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -3570,18 +3570,18 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.167</v>
+        <v>1.1459999999999999</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
       <c r="E7" s="0">
-        <v>-0.50900000000000001</v>
+        <v>-0.51000000000000001</v>
       </c>
       <c r="F7" s="0">
-        <v>53.700000000000003</v>
+        <v>52.200000000000003</v>
       </c>
       <c r="G7" s="0">
-        <v>38.799999999999997</v>
+        <v>37.299999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -3663,9 +3663,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="true"/>
-    <col min="2" max="2" width="6.7109375" customWidth="true"/>
+    <col min="2" max="2" width="7.42578125" customWidth="true"/>
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
-    <col min="4" max="4" width="5.7109375" customWidth="true"/>
+    <col min="4" max="4" width="6.42578125" customWidth="true"/>
     <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
@@ -3691,13 +3691,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>9.7431000000000001</v>
+        <v>9.4717000000000002</v>
       </c>
       <c r="C2" s="0">
-        <v>1.7477</v>
+        <v>1.7285999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>5.5750000000000002</v>
+        <v>5.4800000000000004</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>113</v>
       </c>
       <c r="B3" s="0">
-        <v>0.018100000000000002</v>
+        <v>0.018499999999999999</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0025999999999999999</v>
+        <v>0.0025000000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>7.056</v>
+        <v>7.2939999999999996</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>
@@ -3725,16 +3725,16 @@
         <v>114</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.016</v>
+        <v>-0.0147</v>
       </c>
       <c r="C4" s="0">
-        <v>0.01</v>
+        <v>0.0097999999999999997</v>
       </c>
       <c r="D4" s="0">
-        <v>-1.6000000000000001</v>
+        <v>-1.496</v>
       </c>
       <c r="E4" s="0">
-        <v>0.11459999999999999</v>
+        <v>0.1396</v>
       </c>
     </row>
     <row r="5">
@@ -3742,16 +3742,16 @@
         <v>115</v>
       </c>
       <c r="B5" s="0">
-        <v>0.4229</v>
+        <v>0.41039999999999999</v>
       </c>
       <c r="C5" s="0">
-        <v>0.3377</v>
+        <v>0.33279999999999999</v>
       </c>
       <c r="D5" s="0">
-        <v>1.252</v>
+        <v>1.2330000000000001</v>
       </c>
       <c r="E5" s="0">
-        <v>0.21510000000000001</v>
+        <v>0.22209999999999999</v>
       </c>
     </row>
   </sheetData>
